--- a/data/monthly_place/【2026年7月】月次配置.xlsx
+++ b/data/monthly_place/【2026年7月】月次配置.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4415" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5381" uniqueCount="257">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -650,6 +650,147 @@
   <si>
     <t>2027-07-22</t>
   </si>
+  <si>
+    <t>2027-05-01</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック（2年目）</t>
+  </si>
+  <si>
+    <t>金町駅前ジャスミン歯科（2回目）</t>
+  </si>
+  <si>
+    <t>掛川整体院サウレ</t>
+  </si>
+  <si>
+    <t>鍼灸サロンNOA</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>DesignBody 御徒町店</t>
+  </si>
+  <si>
+    <t>有限会社 ムネケン</t>
+  </si>
+  <si>
+    <t>Healing Salon Ange</t>
+  </si>
+  <si>
+    <t>2026-11-27</t>
+  </si>
+  <si>
+    <t>アキュラデンタルクリニック</t>
+  </si>
+  <si>
+    <t>Beauty Salon Arona</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科</t>
+  </si>
+  <si>
+    <t>UESUGI美容鍼灸整骨院</t>
+  </si>
+  <si>
+    <t>2026-11-03</t>
+  </si>
+  <si>
+    <t>スカイハイ英語塾</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>モバイルウェブ</t>
+  </si>
+  <si>
+    <t>すがや歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>むぎ歯科</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>はま歯科医院</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>整体処 たくみ堂</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>Sheena HEALING SALON</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>千歳烏山ケンズ歯科</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>GAJUM photo studio</t>
+  </si>
+  <si>
+    <t>ストレッチ&amp;ボディケア m.o.v.e巣鴨店</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>割田歯科医院</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（マウスピース矯正）</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>銀座トレーニングラボ</t>
+  </si>
 </sst>
 </file>
 
@@ -999,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB402"/>
+  <dimension ref="A1:AB492"/>
   <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -33802,6 +33943,6879 @@
       </c>
       <c r="AB402">
         <v>212.76923099999999</v>
+      </c>
+    </row>
+    <row r="403" spans="1:28" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>28</v>
+      </c>
+      <c r="B403" t="s">
+        <v>29</v>
+      </c>
+      <c r="C403" t="s">
+        <v>256</v>
+      </c>
+      <c r="D403" t="s">
+        <v>31</v>
+      </c>
+      <c r="E403" t="s">
+        <v>32</v>
+      </c>
+      <c r="F403" t="s">
+        <v>38</v>
+      </c>
+      <c r="G403" t="s">
+        <v>216</v>
+      </c>
+      <c r="H403" t="s">
+        <v>35</v>
+      </c>
+      <c r="K403">
+        <v>10</v>
+      </c>
+      <c r="L403">
+        <v>1</v>
+      </c>
+      <c r="N403" t="s">
+        <v>52</v>
+      </c>
+      <c r="O403">
+        <v>0</v>
+      </c>
+      <c r="P403">
+        <v>12</v>
+      </c>
+      <c r="Q403" t="s">
+        <v>255</v>
+      </c>
+      <c r="R403">
+        <v>10</v>
+      </c>
+      <c r="S403">
+        <v>1200</v>
+      </c>
+      <c r="X403">
+        <v>0</v>
+      </c>
+      <c r="Y403">
+        <v>0</v>
+      </c>
+      <c r="Z403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>28</v>
+      </c>
+      <c r="B404" t="s">
+        <v>29</v>
+      </c>
+      <c r="C404" t="s">
+        <v>256</v>
+      </c>
+      <c r="D404" t="s">
+        <v>31</v>
+      </c>
+      <c r="E404" t="s">
+        <v>41</v>
+      </c>
+      <c r="F404" t="s">
+        <v>38</v>
+      </c>
+      <c r="G404" t="s">
+        <v>216</v>
+      </c>
+      <c r="H404" t="s">
+        <v>35</v>
+      </c>
+      <c r="K404">
+        <v>12</v>
+      </c>
+      <c r="L404">
+        <v>1.1666669999999999</v>
+      </c>
+      <c r="N404" t="s">
+        <v>52</v>
+      </c>
+      <c r="O404">
+        <v>0</v>
+      </c>
+      <c r="P404">
+        <v>29</v>
+      </c>
+      <c r="Q404" t="s">
+        <v>255</v>
+      </c>
+      <c r="R404">
+        <v>14</v>
+      </c>
+      <c r="S404">
+        <v>2071.4285709999999</v>
+      </c>
+      <c r="X404">
+        <v>0</v>
+      </c>
+      <c r="Y404">
+        <v>0</v>
+      </c>
+      <c r="Z404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
+        <v>28</v>
+      </c>
+      <c r="B405" t="s">
+        <v>29</v>
+      </c>
+      <c r="C405" t="s">
+        <v>256</v>
+      </c>
+      <c r="D405" t="s">
+        <v>31</v>
+      </c>
+      <c r="E405" t="s">
+        <v>42</v>
+      </c>
+      <c r="F405" t="s">
+        <v>38</v>
+      </c>
+      <c r="G405" t="s">
+        <v>216</v>
+      </c>
+      <c r="H405" t="s">
+        <v>35</v>
+      </c>
+      <c r="I405">
+        <v>9</v>
+      </c>
+      <c r="J405" t="s">
+        <v>39</v>
+      </c>
+      <c r="K405">
+        <v>334</v>
+      </c>
+      <c r="L405">
+        <v>1.2065870000000001</v>
+      </c>
+      <c r="M405">
+        <v>78.888888890000004</v>
+      </c>
+      <c r="N405" t="s">
+        <v>52</v>
+      </c>
+      <c r="O405">
+        <v>0</v>
+      </c>
+      <c r="P405">
+        <v>710</v>
+      </c>
+      <c r="Q405" t="s">
+        <v>255</v>
+      </c>
+      <c r="R405">
+        <v>403</v>
+      </c>
+      <c r="S405">
+        <v>1761.786601</v>
+      </c>
+      <c r="T405">
+        <v>9</v>
+      </c>
+      <c r="V405">
+        <v>78.888889000000006</v>
+      </c>
+      <c r="W405">
+        <v>2.2332510000000001</v>
+      </c>
+      <c r="X405">
+        <v>9</v>
+      </c>
+      <c r="Y405">
+        <v>2.2332510000000001</v>
+      </c>
+      <c r="Z405">
+        <v>78.888889000000006</v>
+      </c>
+      <c r="AA405">
+        <v>3</v>
+      </c>
+      <c r="AB405">
+        <v>236.66666699999999</v>
+      </c>
+    </row>
+    <row r="406" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
+        <v>28</v>
+      </c>
+      <c r="B406" t="s">
+        <v>29</v>
+      </c>
+      <c r="C406" t="s">
+        <v>254</v>
+      </c>
+      <c r="D406" t="s">
+        <v>31</v>
+      </c>
+      <c r="E406" t="s">
+        <v>32</v>
+      </c>
+      <c r="F406" t="s">
+        <v>38</v>
+      </c>
+      <c r="G406" t="s">
+        <v>216</v>
+      </c>
+      <c r="H406" t="s">
+        <v>35</v>
+      </c>
+      <c r="I406">
+        <v>1</v>
+      </c>
+      <c r="J406" t="s">
+        <v>39</v>
+      </c>
+      <c r="K406">
+        <v>146</v>
+      </c>
+      <c r="L406">
+        <v>1.0068490000000001</v>
+      </c>
+      <c r="M406">
+        <v>138</v>
+      </c>
+      <c r="N406" t="s">
+        <v>52</v>
+      </c>
+      <c r="O406">
+        <v>0</v>
+      </c>
+      <c r="P406">
+        <v>138</v>
+      </c>
+      <c r="Q406" t="s">
+        <v>253</v>
+      </c>
+      <c r="R406">
+        <v>147</v>
+      </c>
+      <c r="S406">
+        <v>938.77551000000005</v>
+      </c>
+      <c r="T406">
+        <v>1</v>
+      </c>
+      <c r="V406">
+        <v>138</v>
+      </c>
+      <c r="W406">
+        <v>0.68027199999999999</v>
+      </c>
+      <c r="X406">
+        <v>1</v>
+      </c>
+      <c r="Y406">
+        <v>0.68027199999999999</v>
+      </c>
+      <c r="Z406">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="407" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
+        <v>28</v>
+      </c>
+      <c r="B407" t="s">
+        <v>29</v>
+      </c>
+      <c r="C407" t="s">
+        <v>254</v>
+      </c>
+      <c r="D407" t="s">
+        <v>31</v>
+      </c>
+      <c r="E407" t="s">
+        <v>41</v>
+      </c>
+      <c r="F407" t="s">
+        <v>38</v>
+      </c>
+      <c r="G407" t="s">
+        <v>216</v>
+      </c>
+      <c r="H407" t="s">
+        <v>35</v>
+      </c>
+      <c r="K407">
+        <v>24</v>
+      </c>
+      <c r="L407">
+        <v>1.0416669999999999</v>
+      </c>
+      <c r="N407" t="s">
+        <v>52</v>
+      </c>
+      <c r="O407">
+        <v>0</v>
+      </c>
+      <c r="P407">
+        <v>17</v>
+      </c>
+      <c r="Q407" t="s">
+        <v>253</v>
+      </c>
+      <c r="R407">
+        <v>25</v>
+      </c>
+      <c r="S407">
+        <v>680</v>
+      </c>
+      <c r="X407">
+        <v>0</v>
+      </c>
+      <c r="Y407">
+        <v>0</v>
+      </c>
+      <c r="Z407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>28</v>
+      </c>
+      <c r="B408" t="s">
+        <v>29</v>
+      </c>
+      <c r="C408" t="s">
+        <v>254</v>
+      </c>
+      <c r="D408" t="s">
+        <v>31</v>
+      </c>
+      <c r="E408" t="s">
+        <v>42</v>
+      </c>
+      <c r="F408" t="s">
+        <v>38</v>
+      </c>
+      <c r="G408" t="s">
+        <v>216</v>
+      </c>
+      <c r="H408" t="s">
+        <v>35</v>
+      </c>
+      <c r="I408">
+        <v>3</v>
+      </c>
+      <c r="J408" t="s">
+        <v>39</v>
+      </c>
+      <c r="K408">
+        <v>201</v>
+      </c>
+      <c r="L408">
+        <v>1.004975</v>
+      </c>
+      <c r="M408">
+        <v>99.666666669999998</v>
+      </c>
+      <c r="N408" t="s">
+        <v>52</v>
+      </c>
+      <c r="O408">
+        <v>0</v>
+      </c>
+      <c r="P408">
+        <v>299</v>
+      </c>
+      <c r="Q408" t="s">
+        <v>253</v>
+      </c>
+      <c r="R408">
+        <v>202</v>
+      </c>
+      <c r="S408">
+        <v>1480.19802</v>
+      </c>
+      <c r="T408">
+        <v>3</v>
+      </c>
+      <c r="V408">
+        <v>99.666667000000004</v>
+      </c>
+      <c r="W408">
+        <v>1.4851490000000001</v>
+      </c>
+      <c r="X408">
+        <v>3</v>
+      </c>
+      <c r="Y408">
+        <v>1.4851490000000001</v>
+      </c>
+      <c r="Z408">
+        <v>99.666667000000004</v>
+      </c>
+      <c r="AA408">
+        <v>2</v>
+      </c>
+      <c r="AB408">
+        <v>149.5</v>
+      </c>
+    </row>
+    <row r="409" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
+        <v>28</v>
+      </c>
+      <c r="B409" t="s">
+        <v>29</v>
+      </c>
+      <c r="C409" t="s">
+        <v>252</v>
+      </c>
+      <c r="D409" t="s">
+        <v>31</v>
+      </c>
+      <c r="E409" t="s">
+        <v>32</v>
+      </c>
+      <c r="F409" t="s">
+        <v>38</v>
+      </c>
+      <c r="G409" t="s">
+        <v>216</v>
+      </c>
+      <c r="H409" t="s">
+        <v>35</v>
+      </c>
+      <c r="I409">
+        <v>1</v>
+      </c>
+      <c r="J409" t="s">
+        <v>39</v>
+      </c>
+      <c r="K409">
+        <v>168</v>
+      </c>
+      <c r="L409">
+        <v>1.0297620000000001</v>
+      </c>
+      <c r="M409">
+        <v>156</v>
+      </c>
+      <c r="N409" t="s">
+        <v>52</v>
+      </c>
+      <c r="O409">
+        <v>0</v>
+      </c>
+      <c r="P409">
+        <v>156</v>
+      </c>
+      <c r="Q409" t="s">
+        <v>250</v>
+      </c>
+      <c r="R409">
+        <v>173</v>
+      </c>
+      <c r="S409">
+        <v>901.734104</v>
+      </c>
+      <c r="T409">
+        <v>1</v>
+      </c>
+      <c r="V409">
+        <v>156</v>
+      </c>
+      <c r="W409">
+        <v>0.57803499999999997</v>
+      </c>
+      <c r="X409">
+        <v>1</v>
+      </c>
+      <c r="Y409">
+        <v>0.57803499999999997</v>
+      </c>
+      <c r="Z409">
+        <v>156</v>
+      </c>
+      <c r="AA409">
+        <v>1</v>
+      </c>
+      <c r="AB409">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="410" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A410" t="s">
+        <v>28</v>
+      </c>
+      <c r="B410" t="s">
+        <v>29</v>
+      </c>
+      <c r="C410" t="s">
+        <v>252</v>
+      </c>
+      <c r="D410" t="s">
+        <v>31</v>
+      </c>
+      <c r="E410" t="s">
+        <v>41</v>
+      </c>
+      <c r="F410" t="s">
+        <v>38</v>
+      </c>
+      <c r="G410" t="s">
+        <v>216</v>
+      </c>
+      <c r="H410" t="s">
+        <v>35</v>
+      </c>
+      <c r="I410">
+        <v>2</v>
+      </c>
+      <c r="J410" t="s">
+        <v>39</v>
+      </c>
+      <c r="K410">
+        <v>36</v>
+      </c>
+      <c r="L410">
+        <v>1.0555559999999999</v>
+      </c>
+      <c r="M410">
+        <v>14.5</v>
+      </c>
+      <c r="N410" t="s">
+        <v>52</v>
+      </c>
+      <c r="O410">
+        <v>0</v>
+      </c>
+      <c r="P410">
+        <v>29</v>
+      </c>
+      <c r="Q410" t="s">
+        <v>250</v>
+      </c>
+      <c r="R410">
+        <v>38</v>
+      </c>
+      <c r="S410">
+        <v>763.15789500000005</v>
+      </c>
+      <c r="T410">
+        <v>2</v>
+      </c>
+      <c r="V410">
+        <v>14.5</v>
+      </c>
+      <c r="W410">
+        <v>5.2631579999999998</v>
+      </c>
+      <c r="X410">
+        <v>3</v>
+      </c>
+      <c r="Y410">
+        <v>7.8947370000000001</v>
+      </c>
+      <c r="Z410">
+        <v>9.6666670000000003</v>
+      </c>
+      <c r="AA410">
+        <v>1</v>
+      </c>
+      <c r="AB410">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="411" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A411" t="s">
+        <v>28</v>
+      </c>
+      <c r="B411" t="s">
+        <v>29</v>
+      </c>
+      <c r="C411" t="s">
+        <v>252</v>
+      </c>
+      <c r="D411" t="s">
+        <v>31</v>
+      </c>
+      <c r="E411" t="s">
+        <v>42</v>
+      </c>
+      <c r="F411" t="s">
+        <v>38</v>
+      </c>
+      <c r="G411" t="s">
+        <v>216</v>
+      </c>
+      <c r="H411" t="s">
+        <v>35</v>
+      </c>
+      <c r="I411">
+        <v>1</v>
+      </c>
+      <c r="J411" t="s">
+        <v>39</v>
+      </c>
+      <c r="K411">
+        <v>150</v>
+      </c>
+      <c r="L411">
+        <v>1.013333</v>
+      </c>
+      <c r="M411">
+        <v>222</v>
+      </c>
+      <c r="N411" t="s">
+        <v>52</v>
+      </c>
+      <c r="O411">
+        <v>0</v>
+      </c>
+      <c r="P411">
+        <v>222</v>
+      </c>
+      <c r="Q411" t="s">
+        <v>250</v>
+      </c>
+      <c r="R411">
+        <v>152</v>
+      </c>
+      <c r="S411">
+        <v>1460.526316</v>
+      </c>
+      <c r="T411">
+        <v>1</v>
+      </c>
+      <c r="V411">
+        <v>222</v>
+      </c>
+      <c r="W411">
+        <v>0.65789500000000001</v>
+      </c>
+      <c r="X411">
+        <v>2</v>
+      </c>
+      <c r="Y411">
+        <v>1.3157890000000001</v>
+      </c>
+      <c r="Z411">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="412" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A412" t="s">
+        <v>28</v>
+      </c>
+      <c r="B412" t="s">
+        <v>29</v>
+      </c>
+      <c r="C412" t="s">
+        <v>251</v>
+      </c>
+      <c r="D412" t="s">
+        <v>31</v>
+      </c>
+      <c r="E412" t="s">
+        <v>32</v>
+      </c>
+      <c r="F412" t="s">
+        <v>38</v>
+      </c>
+      <c r="G412" t="s">
+        <v>216</v>
+      </c>
+      <c r="H412" t="s">
+        <v>35</v>
+      </c>
+      <c r="I412">
+        <v>1</v>
+      </c>
+      <c r="J412" t="s">
+        <v>39</v>
+      </c>
+      <c r="K412">
+        <v>46</v>
+      </c>
+      <c r="L412">
+        <v>1.021739</v>
+      </c>
+      <c r="M412">
+        <v>46</v>
+      </c>
+      <c r="N412" t="s">
+        <v>52</v>
+      </c>
+      <c r="O412">
+        <v>0</v>
+      </c>
+      <c r="P412">
+        <v>46</v>
+      </c>
+      <c r="Q412" t="s">
+        <v>250</v>
+      </c>
+      <c r="R412">
+        <v>47</v>
+      </c>
+      <c r="S412">
+        <v>978.72340399999996</v>
+      </c>
+      <c r="T412">
+        <v>1</v>
+      </c>
+      <c r="V412">
+        <v>46</v>
+      </c>
+      <c r="W412">
+        <v>2.1276600000000001</v>
+      </c>
+      <c r="X412">
+        <v>1</v>
+      </c>
+      <c r="Y412">
+        <v>2.1276600000000001</v>
+      </c>
+      <c r="Z412">
+        <v>46</v>
+      </c>
+      <c r="AA412">
+        <v>1</v>
+      </c>
+      <c r="AB412">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="413" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>28</v>
+      </c>
+      <c r="B413" t="s">
+        <v>29</v>
+      </c>
+      <c r="C413" t="s">
+        <v>251</v>
+      </c>
+      <c r="D413" t="s">
+        <v>31</v>
+      </c>
+      <c r="E413" t="s">
+        <v>41</v>
+      </c>
+      <c r="F413" t="s">
+        <v>38</v>
+      </c>
+      <c r="G413" t="s">
+        <v>216</v>
+      </c>
+      <c r="H413" t="s">
+        <v>35</v>
+      </c>
+      <c r="K413">
+        <v>21</v>
+      </c>
+      <c r="L413">
+        <v>1.0476190000000001</v>
+      </c>
+      <c r="N413" t="s">
+        <v>52</v>
+      </c>
+      <c r="O413">
+        <v>0</v>
+      </c>
+      <c r="P413">
+        <v>21</v>
+      </c>
+      <c r="Q413" t="s">
+        <v>250</v>
+      </c>
+      <c r="R413">
+        <v>22</v>
+      </c>
+      <c r="S413">
+        <v>954.54545499999995</v>
+      </c>
+      <c r="X413">
+        <v>1</v>
+      </c>
+      <c r="Y413">
+        <v>4.5454549999999996</v>
+      </c>
+      <c r="Z413">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="414" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A414" t="s">
+        <v>28</v>
+      </c>
+      <c r="B414" t="s">
+        <v>29</v>
+      </c>
+      <c r="C414" t="s">
+        <v>251</v>
+      </c>
+      <c r="D414" t="s">
+        <v>31</v>
+      </c>
+      <c r="E414" t="s">
+        <v>42</v>
+      </c>
+      <c r="F414" t="s">
+        <v>38</v>
+      </c>
+      <c r="G414" t="s">
+        <v>216</v>
+      </c>
+      <c r="H414" t="s">
+        <v>35</v>
+      </c>
+      <c r="I414">
+        <v>9</v>
+      </c>
+      <c r="J414" t="s">
+        <v>39</v>
+      </c>
+      <c r="K414">
+        <v>257</v>
+      </c>
+      <c r="L414">
+        <v>1.011673</v>
+      </c>
+      <c r="M414">
+        <v>46.666666669999998</v>
+      </c>
+      <c r="N414" t="s">
+        <v>52</v>
+      </c>
+      <c r="O414">
+        <v>0</v>
+      </c>
+      <c r="P414">
+        <v>420</v>
+      </c>
+      <c r="Q414" t="s">
+        <v>250</v>
+      </c>
+      <c r="R414">
+        <v>260</v>
+      </c>
+      <c r="S414">
+        <v>1615.3846149999999</v>
+      </c>
+      <c r="T414">
+        <v>9</v>
+      </c>
+      <c r="V414">
+        <v>46.666666999999997</v>
+      </c>
+      <c r="W414">
+        <v>3.461538</v>
+      </c>
+      <c r="X414">
+        <v>9</v>
+      </c>
+      <c r="Y414">
+        <v>3.461538</v>
+      </c>
+      <c r="Z414">
+        <v>46.666666999999997</v>
+      </c>
+      <c r="AA414">
+        <v>6</v>
+      </c>
+      <c r="AB414">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="415" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>28</v>
+      </c>
+      <c r="B415" t="s">
+        <v>29</v>
+      </c>
+      <c r="C415" t="s">
+        <v>249</v>
+      </c>
+      <c r="D415" t="s">
+        <v>31</v>
+      </c>
+      <c r="E415" t="s">
+        <v>32</v>
+      </c>
+      <c r="F415" t="s">
+        <v>38</v>
+      </c>
+      <c r="G415" t="s">
+        <v>216</v>
+      </c>
+      <c r="H415" t="s">
+        <v>35</v>
+      </c>
+      <c r="I415">
+        <v>11</v>
+      </c>
+      <c r="J415" t="s">
+        <v>39</v>
+      </c>
+      <c r="K415">
+        <v>490</v>
+      </c>
+      <c r="L415">
+        <v>1.1265309999999999</v>
+      </c>
+      <c r="M415">
+        <v>31.09090909</v>
+      </c>
+      <c r="N415" t="s">
+        <v>52</v>
+      </c>
+      <c r="O415">
+        <v>0</v>
+      </c>
+      <c r="P415">
+        <v>342</v>
+      </c>
+      <c r="Q415" t="s">
+        <v>246</v>
+      </c>
+      <c r="R415">
+        <v>552</v>
+      </c>
+      <c r="S415">
+        <v>619.56521699999996</v>
+      </c>
+      <c r="T415">
+        <v>11</v>
+      </c>
+      <c r="V415">
+        <v>31.090909</v>
+      </c>
+      <c r="W415">
+        <v>1.9927539999999999</v>
+      </c>
+      <c r="X415">
+        <v>11</v>
+      </c>
+      <c r="Y415">
+        <v>1.9927539999999999</v>
+      </c>
+      <c r="Z415">
+        <v>31.090909</v>
+      </c>
+      <c r="AA415">
+        <v>8</v>
+      </c>
+      <c r="AB415">
+        <v>42.75</v>
+      </c>
+    </row>
+    <row r="416" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>28</v>
+      </c>
+      <c r="B416" t="s">
+        <v>29</v>
+      </c>
+      <c r="C416" t="s">
+        <v>249</v>
+      </c>
+      <c r="D416" t="s">
+        <v>31</v>
+      </c>
+      <c r="E416" t="s">
+        <v>41</v>
+      </c>
+      <c r="F416" t="s">
+        <v>38</v>
+      </c>
+      <c r="G416" t="s">
+        <v>216</v>
+      </c>
+      <c r="H416" t="s">
+        <v>35</v>
+      </c>
+      <c r="I416">
+        <v>8</v>
+      </c>
+      <c r="J416" t="s">
+        <v>39</v>
+      </c>
+      <c r="K416">
+        <v>244</v>
+      </c>
+      <c r="L416">
+        <v>1.106557</v>
+      </c>
+      <c r="M416">
+        <v>31.875</v>
+      </c>
+      <c r="N416" t="s">
+        <v>52</v>
+      </c>
+      <c r="O416">
+        <v>0</v>
+      </c>
+      <c r="P416">
+        <v>255</v>
+      </c>
+      <c r="Q416" t="s">
+        <v>246</v>
+      </c>
+      <c r="R416">
+        <v>270</v>
+      </c>
+      <c r="S416">
+        <v>944.44444399999998</v>
+      </c>
+      <c r="T416">
+        <v>8</v>
+      </c>
+      <c r="V416">
+        <v>31.875</v>
+      </c>
+      <c r="W416">
+        <v>2.9629629999999998</v>
+      </c>
+      <c r="X416">
+        <v>13</v>
+      </c>
+      <c r="Y416">
+        <v>4.8148150000000003</v>
+      </c>
+      <c r="Z416">
+        <v>19.615385</v>
+      </c>
+      <c r="AA416">
+        <v>7</v>
+      </c>
+      <c r="AB416">
+        <v>36.428570999999998</v>
+      </c>
+    </row>
+    <row r="417" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>28</v>
+      </c>
+      <c r="B417" t="s">
+        <v>29</v>
+      </c>
+      <c r="C417" t="s">
+        <v>249</v>
+      </c>
+      <c r="D417" t="s">
+        <v>31</v>
+      </c>
+      <c r="E417" t="s">
+        <v>42</v>
+      </c>
+      <c r="F417" t="s">
+        <v>38</v>
+      </c>
+      <c r="G417" t="s">
+        <v>216</v>
+      </c>
+      <c r="H417" t="s">
+        <v>35</v>
+      </c>
+      <c r="I417">
+        <v>7</v>
+      </c>
+      <c r="J417" t="s">
+        <v>39</v>
+      </c>
+      <c r="K417">
+        <v>191</v>
+      </c>
+      <c r="L417">
+        <v>1.026178</v>
+      </c>
+      <c r="M417">
+        <v>42.857142860000003</v>
+      </c>
+      <c r="N417" t="s">
+        <v>52</v>
+      </c>
+      <c r="O417">
+        <v>0</v>
+      </c>
+      <c r="P417">
+        <v>300</v>
+      </c>
+      <c r="Q417" t="s">
+        <v>246</v>
+      </c>
+      <c r="R417">
+        <v>196</v>
+      </c>
+      <c r="S417">
+        <v>1530.612245</v>
+      </c>
+      <c r="T417">
+        <v>7</v>
+      </c>
+      <c r="V417">
+        <v>42.857143000000001</v>
+      </c>
+      <c r="W417">
+        <v>3.5714290000000002</v>
+      </c>
+      <c r="X417">
+        <v>7</v>
+      </c>
+      <c r="Y417">
+        <v>3.5714290000000002</v>
+      </c>
+      <c r="Z417">
+        <v>42.857143000000001</v>
+      </c>
+      <c r="AA417">
+        <v>5</v>
+      </c>
+      <c r="AB417">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="418" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A418" t="s">
+        <v>28</v>
+      </c>
+      <c r="B418" t="s">
+        <v>29</v>
+      </c>
+      <c r="C418" t="s">
+        <v>248</v>
+      </c>
+      <c r="D418" t="s">
+        <v>31</v>
+      </c>
+      <c r="E418" t="s">
+        <v>32</v>
+      </c>
+      <c r="F418" t="s">
+        <v>38</v>
+      </c>
+      <c r="G418" t="s">
+        <v>216</v>
+      </c>
+      <c r="H418" t="s">
+        <v>35</v>
+      </c>
+      <c r="I418">
+        <v>11</v>
+      </c>
+      <c r="J418" t="s">
+        <v>39</v>
+      </c>
+      <c r="K418">
+        <v>342</v>
+      </c>
+      <c r="L418">
+        <v>1.0789470000000001</v>
+      </c>
+      <c r="M418">
+        <v>27.09090909</v>
+      </c>
+      <c r="N418" t="s">
+        <v>52</v>
+      </c>
+      <c r="O418">
+        <v>0</v>
+      </c>
+      <c r="P418">
+        <v>298</v>
+      </c>
+      <c r="Q418" t="s">
+        <v>246</v>
+      </c>
+      <c r="R418">
+        <v>369</v>
+      </c>
+      <c r="S418">
+        <v>807.588076</v>
+      </c>
+      <c r="T418">
+        <v>11</v>
+      </c>
+      <c r="V418">
+        <v>27.090909</v>
+      </c>
+      <c r="W418">
+        <v>2.9810300000000001</v>
+      </c>
+      <c r="X418">
+        <v>12</v>
+      </c>
+      <c r="Y418">
+        <v>3.252033</v>
+      </c>
+      <c r="Z418">
+        <v>24.833333</v>
+      </c>
+      <c r="AA418">
+        <v>11</v>
+      </c>
+      <c r="AB418">
+        <v>27.090909</v>
+      </c>
+    </row>
+    <row r="419" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>28</v>
+      </c>
+      <c r="B419" t="s">
+        <v>29</v>
+      </c>
+      <c r="C419" t="s">
+        <v>248</v>
+      </c>
+      <c r="D419" t="s">
+        <v>31</v>
+      </c>
+      <c r="E419" t="s">
+        <v>41</v>
+      </c>
+      <c r="F419" t="s">
+        <v>38</v>
+      </c>
+      <c r="G419" t="s">
+        <v>216</v>
+      </c>
+      <c r="H419" t="s">
+        <v>35</v>
+      </c>
+      <c r="I419">
+        <v>4</v>
+      </c>
+      <c r="J419" t="s">
+        <v>39</v>
+      </c>
+      <c r="K419">
+        <v>179</v>
+      </c>
+      <c r="L419">
+        <v>1.1005590000000001</v>
+      </c>
+      <c r="M419">
+        <v>45.5</v>
+      </c>
+      <c r="N419" t="s">
+        <v>52</v>
+      </c>
+      <c r="O419">
+        <v>0</v>
+      </c>
+      <c r="P419">
+        <v>182</v>
+      </c>
+      <c r="Q419" t="s">
+        <v>246</v>
+      </c>
+      <c r="R419">
+        <v>197</v>
+      </c>
+      <c r="S419">
+        <v>923.85786800000005</v>
+      </c>
+      <c r="T419">
+        <v>4</v>
+      </c>
+      <c r="V419">
+        <v>45.5</v>
+      </c>
+      <c r="W419">
+        <v>2.0304570000000002</v>
+      </c>
+      <c r="X419">
+        <v>5</v>
+      </c>
+      <c r="Y419">
+        <v>2.538071</v>
+      </c>
+      <c r="Z419">
+        <v>36.4</v>
+      </c>
+      <c r="AA419">
+        <v>3</v>
+      </c>
+      <c r="AB419">
+        <v>60.666666999999997</v>
+      </c>
+    </row>
+    <row r="420" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
+        <v>28</v>
+      </c>
+      <c r="B420" t="s">
+        <v>29</v>
+      </c>
+      <c r="C420" t="s">
+        <v>248</v>
+      </c>
+      <c r="D420" t="s">
+        <v>31</v>
+      </c>
+      <c r="E420" t="s">
+        <v>42</v>
+      </c>
+      <c r="F420" t="s">
+        <v>38</v>
+      </c>
+      <c r="G420" t="s">
+        <v>216</v>
+      </c>
+      <c r="H420" t="s">
+        <v>35</v>
+      </c>
+      <c r="I420">
+        <v>9</v>
+      </c>
+      <c r="J420" t="s">
+        <v>39</v>
+      </c>
+      <c r="K420">
+        <v>195</v>
+      </c>
+      <c r="L420">
+        <v>1.0358970000000001</v>
+      </c>
+      <c r="M420">
+        <v>46</v>
+      </c>
+      <c r="N420" t="s">
+        <v>52</v>
+      </c>
+      <c r="O420">
+        <v>0</v>
+      </c>
+      <c r="P420">
+        <v>414</v>
+      </c>
+      <c r="Q420" t="s">
+        <v>246</v>
+      </c>
+      <c r="R420">
+        <v>202</v>
+      </c>
+      <c r="S420">
+        <v>2049.5049509999999</v>
+      </c>
+      <c r="T420">
+        <v>9</v>
+      </c>
+      <c r="V420">
+        <v>46</v>
+      </c>
+      <c r="W420">
+        <v>4.4554460000000002</v>
+      </c>
+      <c r="X420">
+        <v>10</v>
+      </c>
+      <c r="Y420">
+        <v>4.9504950000000001</v>
+      </c>
+      <c r="Z420">
+        <v>41.4</v>
+      </c>
+      <c r="AA420">
+        <v>7</v>
+      </c>
+      <c r="AB420">
+        <v>59.142856999999999</v>
+      </c>
+    </row>
+    <row r="421" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>28</v>
+      </c>
+      <c r="B421" t="s">
+        <v>29</v>
+      </c>
+      <c r="C421" t="s">
+        <v>247</v>
+      </c>
+      <c r="D421" t="s">
+        <v>31</v>
+      </c>
+      <c r="E421" t="s">
+        <v>32</v>
+      </c>
+      <c r="F421" t="s">
+        <v>38</v>
+      </c>
+      <c r="G421" t="s">
+        <v>216</v>
+      </c>
+      <c r="H421" t="s">
+        <v>35</v>
+      </c>
+      <c r="K421">
+        <v>40</v>
+      </c>
+      <c r="L421">
+        <v>1.0249999999999999</v>
+      </c>
+      <c r="N421" t="s">
+        <v>52</v>
+      </c>
+      <c r="O421">
+        <v>0</v>
+      </c>
+      <c r="P421">
+        <v>25</v>
+      </c>
+      <c r="Q421" t="s">
+        <v>246</v>
+      </c>
+      <c r="R421">
+        <v>41</v>
+      </c>
+      <c r="S421">
+        <v>609.75609799999995</v>
+      </c>
+      <c r="X421">
+        <v>0</v>
+      </c>
+      <c r="Y421">
+        <v>0</v>
+      </c>
+      <c r="Z421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>28</v>
+      </c>
+      <c r="B422" t="s">
+        <v>29</v>
+      </c>
+      <c r="C422" t="s">
+        <v>247</v>
+      </c>
+      <c r="D422" t="s">
+        <v>31</v>
+      </c>
+      <c r="E422" t="s">
+        <v>41</v>
+      </c>
+      <c r="F422" t="s">
+        <v>38</v>
+      </c>
+      <c r="G422" t="s">
+        <v>216</v>
+      </c>
+      <c r="H422" t="s">
+        <v>35</v>
+      </c>
+      <c r="K422">
+        <v>16</v>
+      </c>
+      <c r="L422">
+        <v>1</v>
+      </c>
+      <c r="N422" t="s">
+        <v>52</v>
+      </c>
+      <c r="O422">
+        <v>0</v>
+      </c>
+      <c r="P422">
+        <v>14</v>
+      </c>
+      <c r="Q422" t="s">
+        <v>246</v>
+      </c>
+      <c r="R422">
+        <v>16</v>
+      </c>
+      <c r="S422">
+        <v>875</v>
+      </c>
+      <c r="X422">
+        <v>0</v>
+      </c>
+      <c r="Y422">
+        <v>0</v>
+      </c>
+      <c r="Z422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>28</v>
+      </c>
+      <c r="B423" t="s">
+        <v>29</v>
+      </c>
+      <c r="C423" t="s">
+        <v>247</v>
+      </c>
+      <c r="D423" t="s">
+        <v>31</v>
+      </c>
+      <c r="E423" t="s">
+        <v>42</v>
+      </c>
+      <c r="F423" t="s">
+        <v>38</v>
+      </c>
+      <c r="G423" t="s">
+        <v>216</v>
+      </c>
+      <c r="H423" t="s">
+        <v>35</v>
+      </c>
+      <c r="I423">
+        <v>23</v>
+      </c>
+      <c r="J423" t="s">
+        <v>39</v>
+      </c>
+      <c r="K423">
+        <v>319</v>
+      </c>
+      <c r="L423">
+        <v>1.021944</v>
+      </c>
+      <c r="M423">
+        <v>27.043478260000001</v>
+      </c>
+      <c r="N423" t="s">
+        <v>52</v>
+      </c>
+      <c r="O423">
+        <v>0</v>
+      </c>
+      <c r="P423">
+        <v>622</v>
+      </c>
+      <c r="Q423" t="s">
+        <v>246</v>
+      </c>
+      <c r="R423">
+        <v>326</v>
+      </c>
+      <c r="S423">
+        <v>1907.9754600000001</v>
+      </c>
+      <c r="T423">
+        <v>23</v>
+      </c>
+      <c r="V423">
+        <v>27.043478</v>
+      </c>
+      <c r="W423">
+        <v>7.0552149999999996</v>
+      </c>
+      <c r="X423">
+        <v>23</v>
+      </c>
+      <c r="Y423">
+        <v>7.0552149999999996</v>
+      </c>
+      <c r="Z423">
+        <v>27.043478</v>
+      </c>
+      <c r="AA423">
+        <v>14</v>
+      </c>
+      <c r="AB423">
+        <v>44.428570999999998</v>
+      </c>
+    </row>
+    <row r="424" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>28</v>
+      </c>
+      <c r="B424" t="s">
+        <v>29</v>
+      </c>
+      <c r="C424" t="s">
+        <v>245</v>
+      </c>
+      <c r="D424" t="s">
+        <v>31</v>
+      </c>
+      <c r="E424" t="s">
+        <v>32</v>
+      </c>
+      <c r="F424" t="s">
+        <v>38</v>
+      </c>
+      <c r="G424" t="s">
+        <v>216</v>
+      </c>
+      <c r="H424" t="s">
+        <v>35</v>
+      </c>
+      <c r="I424">
+        <v>14</v>
+      </c>
+      <c r="J424" t="s">
+        <v>39</v>
+      </c>
+      <c r="K424">
+        <v>681</v>
+      </c>
+      <c r="L424">
+        <v>1.092511</v>
+      </c>
+      <c r="M424">
+        <v>28.071428569999998</v>
+      </c>
+      <c r="N424" t="s">
+        <v>52</v>
+      </c>
+      <c r="O424">
+        <v>0</v>
+      </c>
+      <c r="P424">
+        <v>393</v>
+      </c>
+      <c r="Q424" t="s">
+        <v>244</v>
+      </c>
+      <c r="R424">
+        <v>744</v>
+      </c>
+      <c r="S424">
+        <v>528.22580600000003</v>
+      </c>
+      <c r="T424">
+        <v>14</v>
+      </c>
+      <c r="V424">
+        <v>28.071428999999998</v>
+      </c>
+      <c r="W424">
+        <v>1.8817200000000001</v>
+      </c>
+      <c r="X424">
+        <v>14</v>
+      </c>
+      <c r="Y424">
+        <v>1.8817200000000001</v>
+      </c>
+      <c r="Z424">
+        <v>28.071428999999998</v>
+      </c>
+      <c r="AA424">
+        <v>10</v>
+      </c>
+      <c r="AB424">
+        <v>39.299999999999997</v>
+      </c>
+    </row>
+    <row r="425" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>28</v>
+      </c>
+      <c r="B425" t="s">
+        <v>29</v>
+      </c>
+      <c r="C425" t="s">
+        <v>245</v>
+      </c>
+      <c r="D425" t="s">
+        <v>31</v>
+      </c>
+      <c r="E425" t="s">
+        <v>41</v>
+      </c>
+      <c r="F425" t="s">
+        <v>38</v>
+      </c>
+      <c r="G425" t="s">
+        <v>216</v>
+      </c>
+      <c r="H425" t="s">
+        <v>35</v>
+      </c>
+      <c r="I425">
+        <v>1</v>
+      </c>
+      <c r="J425" t="s">
+        <v>39</v>
+      </c>
+      <c r="K425">
+        <v>11</v>
+      </c>
+      <c r="L425">
+        <v>1.181818</v>
+      </c>
+      <c r="M425">
+        <v>31</v>
+      </c>
+      <c r="N425" t="s">
+        <v>52</v>
+      </c>
+      <c r="O425">
+        <v>0</v>
+      </c>
+      <c r="P425">
+        <v>31</v>
+      </c>
+      <c r="Q425" t="s">
+        <v>244</v>
+      </c>
+      <c r="R425">
+        <v>13</v>
+      </c>
+      <c r="S425">
+        <v>2384.6153850000001</v>
+      </c>
+      <c r="T425">
+        <v>1</v>
+      </c>
+      <c r="V425">
+        <v>31</v>
+      </c>
+      <c r="W425">
+        <v>7.6923079999999997</v>
+      </c>
+      <c r="X425">
+        <v>1</v>
+      </c>
+      <c r="Y425">
+        <v>7.6923079999999997</v>
+      </c>
+      <c r="Z425">
+        <v>31</v>
+      </c>
+      <c r="AA425">
+        <v>1</v>
+      </c>
+      <c r="AB425">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="426" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>28</v>
+      </c>
+      <c r="B426" t="s">
+        <v>29</v>
+      </c>
+      <c r="C426" t="s">
+        <v>245</v>
+      </c>
+      <c r="D426" t="s">
+        <v>31</v>
+      </c>
+      <c r="E426" t="s">
+        <v>42</v>
+      </c>
+      <c r="F426" t="s">
+        <v>38</v>
+      </c>
+      <c r="G426" t="s">
+        <v>216</v>
+      </c>
+      <c r="H426" t="s">
+        <v>35</v>
+      </c>
+      <c r="I426">
+        <v>8</v>
+      </c>
+      <c r="J426" t="s">
+        <v>39</v>
+      </c>
+      <c r="K426">
+        <v>148</v>
+      </c>
+      <c r="L426">
+        <v>1</v>
+      </c>
+      <c r="M426">
+        <v>45</v>
+      </c>
+      <c r="N426" t="s">
+        <v>52</v>
+      </c>
+      <c r="O426">
+        <v>0</v>
+      </c>
+      <c r="P426">
+        <v>360</v>
+      </c>
+      <c r="Q426" t="s">
+        <v>244</v>
+      </c>
+      <c r="R426">
+        <v>148</v>
+      </c>
+      <c r="S426">
+        <v>2432.4324320000001</v>
+      </c>
+      <c r="T426">
+        <v>8</v>
+      </c>
+      <c r="V426">
+        <v>45</v>
+      </c>
+      <c r="W426">
+        <v>5.405405</v>
+      </c>
+      <c r="X426">
+        <v>8</v>
+      </c>
+      <c r="Y426">
+        <v>5.405405</v>
+      </c>
+      <c r="Z426">
+        <v>45</v>
+      </c>
+      <c r="AA426">
+        <v>9</v>
+      </c>
+      <c r="AB426">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="427" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>28</v>
+      </c>
+      <c r="B427" t="s">
+        <v>29</v>
+      </c>
+      <c r="C427" t="s">
+        <v>243</v>
+      </c>
+      <c r="D427" t="s">
+        <v>31</v>
+      </c>
+      <c r="E427" t="s">
+        <v>32</v>
+      </c>
+      <c r="F427" t="s">
+        <v>38</v>
+      </c>
+      <c r="G427" t="s">
+        <v>216</v>
+      </c>
+      <c r="H427" t="s">
+        <v>35</v>
+      </c>
+      <c r="I427">
+        <v>4</v>
+      </c>
+      <c r="J427" t="s">
+        <v>39</v>
+      </c>
+      <c r="K427">
+        <v>305</v>
+      </c>
+      <c r="L427">
+        <v>1.0426230000000001</v>
+      </c>
+      <c r="M427">
+        <v>56.25</v>
+      </c>
+      <c r="N427" t="s">
+        <v>52</v>
+      </c>
+      <c r="O427">
+        <v>0</v>
+      </c>
+      <c r="P427">
+        <v>225</v>
+      </c>
+      <c r="Q427" t="s">
+        <v>241</v>
+      </c>
+      <c r="R427">
+        <v>318</v>
+      </c>
+      <c r="S427">
+        <v>707.54717000000005</v>
+      </c>
+      <c r="T427">
+        <v>4</v>
+      </c>
+      <c r="V427">
+        <v>56.25</v>
+      </c>
+      <c r="W427">
+        <v>1.257862</v>
+      </c>
+      <c r="X427">
+        <v>6</v>
+      </c>
+      <c r="Y427">
+        <v>1.886792</v>
+      </c>
+      <c r="Z427">
+        <v>37.5</v>
+      </c>
+      <c r="AA427">
+        <v>3</v>
+      </c>
+      <c r="AB427">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="428" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>28</v>
+      </c>
+      <c r="B428" t="s">
+        <v>29</v>
+      </c>
+      <c r="C428" t="s">
+        <v>243</v>
+      </c>
+      <c r="D428" t="s">
+        <v>31</v>
+      </c>
+      <c r="E428" t="s">
+        <v>41</v>
+      </c>
+      <c r="F428" t="s">
+        <v>38</v>
+      </c>
+      <c r="G428" t="s">
+        <v>216</v>
+      </c>
+      <c r="H428" t="s">
+        <v>35</v>
+      </c>
+      <c r="I428">
+        <v>5</v>
+      </c>
+      <c r="J428" t="s">
+        <v>39</v>
+      </c>
+      <c r="K428">
+        <v>125</v>
+      </c>
+      <c r="L428">
+        <v>1.0880000000000001</v>
+      </c>
+      <c r="M428">
+        <v>30.6</v>
+      </c>
+      <c r="N428" t="s">
+        <v>52</v>
+      </c>
+      <c r="O428">
+        <v>0</v>
+      </c>
+      <c r="P428">
+        <v>153</v>
+      </c>
+      <c r="Q428" t="s">
+        <v>241</v>
+      </c>
+      <c r="R428">
+        <v>136</v>
+      </c>
+      <c r="S428">
+        <v>1125</v>
+      </c>
+      <c r="T428">
+        <v>5</v>
+      </c>
+      <c r="V428">
+        <v>30.6</v>
+      </c>
+      <c r="W428">
+        <v>3.6764709999999998</v>
+      </c>
+      <c r="X428">
+        <v>7</v>
+      </c>
+      <c r="Y428">
+        <v>5.1470589999999996</v>
+      </c>
+      <c r="Z428">
+        <v>21.857143000000001</v>
+      </c>
+      <c r="AA428">
+        <v>5</v>
+      </c>
+      <c r="AB428">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="429" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>28</v>
+      </c>
+      <c r="B429" t="s">
+        <v>29</v>
+      </c>
+      <c r="C429" t="s">
+        <v>243</v>
+      </c>
+      <c r="D429" t="s">
+        <v>31</v>
+      </c>
+      <c r="E429" t="s">
+        <v>42</v>
+      </c>
+      <c r="F429" t="s">
+        <v>38</v>
+      </c>
+      <c r="G429" t="s">
+        <v>216</v>
+      </c>
+      <c r="H429" t="s">
+        <v>35</v>
+      </c>
+      <c r="I429">
+        <v>23</v>
+      </c>
+      <c r="J429" t="s">
+        <v>39</v>
+      </c>
+      <c r="K429">
+        <v>668</v>
+      </c>
+      <c r="L429">
+        <v>1.0464070000000001</v>
+      </c>
+      <c r="M429">
+        <v>48.086956520000001</v>
+      </c>
+      <c r="N429" t="s">
+        <v>52</v>
+      </c>
+      <c r="O429">
+        <v>0</v>
+      </c>
+      <c r="P429">
+        <v>1106</v>
+      </c>
+      <c r="Q429" t="s">
+        <v>241</v>
+      </c>
+      <c r="R429">
+        <v>699</v>
+      </c>
+      <c r="S429">
+        <v>1582.260372</v>
+      </c>
+      <c r="T429">
+        <v>23</v>
+      </c>
+      <c r="V429">
+        <v>48.086956999999998</v>
+      </c>
+      <c r="W429">
+        <v>3.2904149999999999</v>
+      </c>
+      <c r="X429">
+        <v>24</v>
+      </c>
+      <c r="Y429">
+        <v>3.4334760000000002</v>
+      </c>
+      <c r="Z429">
+        <v>46.083333000000003</v>
+      </c>
+      <c r="AA429">
+        <v>19</v>
+      </c>
+      <c r="AB429">
+        <v>58.210526000000002</v>
+      </c>
+    </row>
+    <row r="430" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>28</v>
+      </c>
+      <c r="B430" t="s">
+        <v>29</v>
+      </c>
+      <c r="C430" t="s">
+        <v>242</v>
+      </c>
+      <c r="D430" t="s">
+        <v>31</v>
+      </c>
+      <c r="E430" t="s">
+        <v>32</v>
+      </c>
+      <c r="F430" t="s">
+        <v>38</v>
+      </c>
+      <c r="G430" t="s">
+        <v>216</v>
+      </c>
+      <c r="H430" t="s">
+        <v>35</v>
+      </c>
+      <c r="I430">
+        <v>7</v>
+      </c>
+      <c r="J430" t="s">
+        <v>39</v>
+      </c>
+      <c r="K430">
+        <v>306</v>
+      </c>
+      <c r="L430">
+        <v>1.03268</v>
+      </c>
+      <c r="M430">
+        <v>40.285714290000001</v>
+      </c>
+      <c r="N430" t="s">
+        <v>52</v>
+      </c>
+      <c r="O430">
+        <v>0</v>
+      </c>
+      <c r="P430">
+        <v>282</v>
+      </c>
+      <c r="Q430" t="s">
+        <v>241</v>
+      </c>
+      <c r="R430">
+        <v>316</v>
+      </c>
+      <c r="S430">
+        <v>892.40506300000004</v>
+      </c>
+      <c r="T430">
+        <v>7</v>
+      </c>
+      <c r="V430">
+        <v>40.285713999999999</v>
+      </c>
+      <c r="W430">
+        <v>2.2151900000000002</v>
+      </c>
+      <c r="X430">
+        <v>6</v>
+      </c>
+      <c r="Y430">
+        <v>1.8987339999999999</v>
+      </c>
+      <c r="Z430">
+        <v>47</v>
+      </c>
+      <c r="AA430">
+        <v>6</v>
+      </c>
+      <c r="AB430">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="431" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A431" t="s">
+        <v>28</v>
+      </c>
+      <c r="B431" t="s">
+        <v>29</v>
+      </c>
+      <c r="C431" t="s">
+        <v>242</v>
+      </c>
+      <c r="D431" t="s">
+        <v>31</v>
+      </c>
+      <c r="E431" t="s">
+        <v>41</v>
+      </c>
+      <c r="F431" t="s">
+        <v>38</v>
+      </c>
+      <c r="G431" t="s">
+        <v>216</v>
+      </c>
+      <c r="H431" t="s">
+        <v>35</v>
+      </c>
+      <c r="K431">
+        <v>11</v>
+      </c>
+      <c r="L431">
+        <v>1.0909089999999999</v>
+      </c>
+      <c r="N431" t="s">
+        <v>52</v>
+      </c>
+      <c r="O431">
+        <v>0</v>
+      </c>
+      <c r="P431">
+        <v>15</v>
+      </c>
+      <c r="Q431" t="s">
+        <v>241</v>
+      </c>
+      <c r="R431">
+        <v>12</v>
+      </c>
+      <c r="S431">
+        <v>1250</v>
+      </c>
+      <c r="X431">
+        <v>0</v>
+      </c>
+      <c r="Y431">
+        <v>0</v>
+      </c>
+      <c r="Z431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>28</v>
+      </c>
+      <c r="B432" t="s">
+        <v>29</v>
+      </c>
+      <c r="C432" t="s">
+        <v>242</v>
+      </c>
+      <c r="D432" t="s">
+        <v>31</v>
+      </c>
+      <c r="E432" t="s">
+        <v>42</v>
+      </c>
+      <c r="F432" t="s">
+        <v>38</v>
+      </c>
+      <c r="G432" t="s">
+        <v>216</v>
+      </c>
+      <c r="H432" t="s">
+        <v>35</v>
+      </c>
+      <c r="I432">
+        <v>42</v>
+      </c>
+      <c r="J432" t="s">
+        <v>39</v>
+      </c>
+      <c r="K432">
+        <v>1721</v>
+      </c>
+      <c r="L432">
+        <v>1.0737939999999999</v>
+      </c>
+      <c r="M432">
+        <v>46.47619048</v>
+      </c>
+      <c r="N432" t="s">
+        <v>52</v>
+      </c>
+      <c r="O432">
+        <v>0</v>
+      </c>
+      <c r="P432">
+        <v>1952</v>
+      </c>
+      <c r="Q432" t="s">
+        <v>241</v>
+      </c>
+      <c r="R432">
+        <v>1848</v>
+      </c>
+      <c r="S432">
+        <v>1056.2770559999999</v>
+      </c>
+      <c r="T432">
+        <v>42</v>
+      </c>
+      <c r="V432">
+        <v>46.476190000000003</v>
+      </c>
+      <c r="W432">
+        <v>2.2727270000000002</v>
+      </c>
+      <c r="X432">
+        <v>44</v>
+      </c>
+      <c r="Y432">
+        <v>2.3809520000000002</v>
+      </c>
+      <c r="Z432">
+        <v>44.363636</v>
+      </c>
+      <c r="AA432">
+        <v>31</v>
+      </c>
+      <c r="AB432">
+        <v>62.967742000000001</v>
+      </c>
+    </row>
+    <row r="433" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A433" t="s">
+        <v>28</v>
+      </c>
+      <c r="B433" t="s">
+        <v>29</v>
+      </c>
+      <c r="C433" t="s">
+        <v>240</v>
+      </c>
+      <c r="D433" t="s">
+        <v>31</v>
+      </c>
+      <c r="E433" t="s">
+        <v>32</v>
+      </c>
+      <c r="F433" t="s">
+        <v>38</v>
+      </c>
+      <c r="G433" t="s">
+        <v>216</v>
+      </c>
+      <c r="H433" t="s">
+        <v>35</v>
+      </c>
+      <c r="I433">
+        <v>5</v>
+      </c>
+      <c r="J433" t="s">
+        <v>39</v>
+      </c>
+      <c r="K433">
+        <v>308</v>
+      </c>
+      <c r="L433">
+        <v>1.074675</v>
+      </c>
+      <c r="M433">
+        <v>54.6</v>
+      </c>
+      <c r="N433" t="s">
+        <v>52</v>
+      </c>
+      <c r="O433">
+        <v>0</v>
+      </c>
+      <c r="P433">
+        <v>273</v>
+      </c>
+      <c r="Q433" t="s">
+        <v>239</v>
+      </c>
+      <c r="R433">
+        <v>331</v>
+      </c>
+      <c r="S433">
+        <v>824.773414</v>
+      </c>
+      <c r="T433">
+        <v>5</v>
+      </c>
+      <c r="V433">
+        <v>54.6</v>
+      </c>
+      <c r="W433">
+        <v>1.5105740000000001</v>
+      </c>
+      <c r="X433">
+        <v>5</v>
+      </c>
+      <c r="Y433">
+        <v>1.5105740000000001</v>
+      </c>
+      <c r="Z433">
+        <v>54.6</v>
+      </c>
+      <c r="AA433">
+        <v>4</v>
+      </c>
+      <c r="AB433">
+        <v>68.25</v>
+      </c>
+    </row>
+    <row r="434" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>28</v>
+      </c>
+      <c r="B434" t="s">
+        <v>29</v>
+      </c>
+      <c r="C434" t="s">
+        <v>240</v>
+      </c>
+      <c r="D434" t="s">
+        <v>31</v>
+      </c>
+      <c r="E434" t="s">
+        <v>41</v>
+      </c>
+      <c r="F434" t="s">
+        <v>38</v>
+      </c>
+      <c r="G434" t="s">
+        <v>216</v>
+      </c>
+      <c r="H434" t="s">
+        <v>35</v>
+      </c>
+      <c r="K434">
+        <v>61</v>
+      </c>
+      <c r="L434">
+        <v>1.2622949999999999</v>
+      </c>
+      <c r="N434" t="s">
+        <v>52</v>
+      </c>
+      <c r="O434">
+        <v>0</v>
+      </c>
+      <c r="P434">
+        <v>81</v>
+      </c>
+      <c r="Q434" t="s">
+        <v>239</v>
+      </c>
+      <c r="R434">
+        <v>77</v>
+      </c>
+      <c r="S434">
+        <v>1051.948052</v>
+      </c>
+      <c r="X434">
+        <v>3</v>
+      </c>
+      <c r="Y434">
+        <v>3.8961039999999998</v>
+      </c>
+      <c r="Z434">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="435" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>28</v>
+      </c>
+      <c r="B435" t="s">
+        <v>29</v>
+      </c>
+      <c r="C435" t="s">
+        <v>240</v>
+      </c>
+      <c r="D435" t="s">
+        <v>31</v>
+      </c>
+      <c r="E435" t="s">
+        <v>42</v>
+      </c>
+      <c r="F435" t="s">
+        <v>38</v>
+      </c>
+      <c r="G435" t="s">
+        <v>216</v>
+      </c>
+      <c r="H435" t="s">
+        <v>35</v>
+      </c>
+      <c r="I435">
+        <v>31</v>
+      </c>
+      <c r="J435" t="s">
+        <v>39</v>
+      </c>
+      <c r="K435">
+        <v>1414</v>
+      </c>
+      <c r="L435">
+        <v>1.061528</v>
+      </c>
+      <c r="M435">
+        <v>56.935483869999999</v>
+      </c>
+      <c r="N435" t="s">
+        <v>52</v>
+      </c>
+      <c r="O435">
+        <v>0</v>
+      </c>
+      <c r="P435">
+        <v>1765</v>
+      </c>
+      <c r="Q435" t="s">
+        <v>239</v>
+      </c>
+      <c r="R435">
+        <v>1501</v>
+      </c>
+      <c r="S435">
+        <v>1175.8827450000001</v>
+      </c>
+      <c r="T435">
+        <v>31</v>
+      </c>
+      <c r="V435">
+        <v>56.935484000000002</v>
+      </c>
+      <c r="W435">
+        <v>2.0652900000000001</v>
+      </c>
+      <c r="X435">
+        <v>31</v>
+      </c>
+      <c r="Y435">
+        <v>2.0652900000000001</v>
+      </c>
+      <c r="Z435">
+        <v>56.935484000000002</v>
+      </c>
+      <c r="AA435">
+        <v>19</v>
+      </c>
+      <c r="AB435">
+        <v>92.894737000000006</v>
+      </c>
+    </row>
+    <row r="436" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A436" t="s">
+        <v>28</v>
+      </c>
+      <c r="B436" t="s">
+        <v>29</v>
+      </c>
+      <c r="C436" t="s">
+        <v>238</v>
+      </c>
+      <c r="D436" t="s">
+        <v>31</v>
+      </c>
+      <c r="E436" t="s">
+        <v>32</v>
+      </c>
+      <c r="F436" t="s">
+        <v>38</v>
+      </c>
+      <c r="G436" t="s">
+        <v>34</v>
+      </c>
+      <c r="H436" t="s">
+        <v>35</v>
+      </c>
+      <c r="I436">
+        <v>5</v>
+      </c>
+      <c r="J436" t="s">
+        <v>39</v>
+      </c>
+      <c r="K436">
+        <v>144</v>
+      </c>
+      <c r="L436">
+        <v>1.1805559999999999</v>
+      </c>
+      <c r="M436">
+        <v>31.2</v>
+      </c>
+      <c r="N436" t="s">
+        <v>52</v>
+      </c>
+      <c r="O436">
+        <v>0</v>
+      </c>
+      <c r="P436">
+        <v>156</v>
+      </c>
+      <c r="Q436" t="s">
+        <v>237</v>
+      </c>
+      <c r="R436">
+        <v>170</v>
+      </c>
+      <c r="S436">
+        <v>917.64705900000001</v>
+      </c>
+      <c r="T436">
+        <v>5</v>
+      </c>
+      <c r="V436">
+        <v>31.2</v>
+      </c>
+      <c r="W436">
+        <v>2.941176</v>
+      </c>
+      <c r="X436">
+        <v>8</v>
+      </c>
+      <c r="Y436">
+        <v>4.7058819999999999</v>
+      </c>
+      <c r="Z436">
+        <v>19.5</v>
+      </c>
+      <c r="AA436">
+        <v>4</v>
+      </c>
+      <c r="AB436">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="437" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>28</v>
+      </c>
+      <c r="B437" t="s">
+        <v>29</v>
+      </c>
+      <c r="C437" t="s">
+        <v>238</v>
+      </c>
+      <c r="D437" t="s">
+        <v>31</v>
+      </c>
+      <c r="E437" t="s">
+        <v>41</v>
+      </c>
+      <c r="F437" t="s">
+        <v>38</v>
+      </c>
+      <c r="G437" t="s">
+        <v>34</v>
+      </c>
+      <c r="H437" t="s">
+        <v>35</v>
+      </c>
+      <c r="K437">
+        <v>34</v>
+      </c>
+      <c r="L437">
+        <v>1.0882350000000001</v>
+      </c>
+      <c r="N437" t="s">
+        <v>52</v>
+      </c>
+      <c r="O437">
+        <v>0</v>
+      </c>
+      <c r="P437">
+        <v>31</v>
+      </c>
+      <c r="Q437" t="s">
+        <v>237</v>
+      </c>
+      <c r="R437">
+        <v>37</v>
+      </c>
+      <c r="S437">
+        <v>837.83783800000003</v>
+      </c>
+      <c r="X437">
+        <v>0</v>
+      </c>
+      <c r="Y437">
+        <v>0</v>
+      </c>
+      <c r="Z437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
+        <v>28</v>
+      </c>
+      <c r="B438" t="s">
+        <v>29</v>
+      </c>
+      <c r="C438" t="s">
+        <v>238</v>
+      </c>
+      <c r="D438" t="s">
+        <v>31</v>
+      </c>
+      <c r="E438" t="s">
+        <v>42</v>
+      </c>
+      <c r="F438" t="s">
+        <v>38</v>
+      </c>
+      <c r="G438" t="s">
+        <v>34</v>
+      </c>
+      <c r="H438" t="s">
+        <v>35</v>
+      </c>
+      <c r="I438">
+        <v>75</v>
+      </c>
+      <c r="J438" t="s">
+        <v>39</v>
+      </c>
+      <c r="K438">
+        <v>2252</v>
+      </c>
+      <c r="L438">
+        <v>1.0595030000000001</v>
+      </c>
+      <c r="M438">
+        <v>38.92</v>
+      </c>
+      <c r="N438" t="s">
+        <v>52</v>
+      </c>
+      <c r="O438">
+        <v>0</v>
+      </c>
+      <c r="P438">
+        <v>2919</v>
+      </c>
+      <c r="Q438" t="s">
+        <v>237</v>
+      </c>
+      <c r="R438">
+        <v>2386</v>
+      </c>
+      <c r="S438">
+        <v>1223.3864209999999</v>
+      </c>
+      <c r="T438">
+        <v>75</v>
+      </c>
+      <c r="V438">
+        <v>38.92</v>
+      </c>
+      <c r="W438">
+        <v>3.1433360000000001</v>
+      </c>
+      <c r="X438">
+        <v>78</v>
+      </c>
+      <c r="Y438">
+        <v>3.2690700000000001</v>
+      </c>
+      <c r="Z438">
+        <v>37.423076999999999</v>
+      </c>
+      <c r="AA438">
+        <v>47</v>
+      </c>
+      <c r="AB438">
+        <v>62.106383000000001</v>
+      </c>
+    </row>
+    <row r="439" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A439" t="s">
+        <v>28</v>
+      </c>
+      <c r="B439" t="s">
+        <v>29</v>
+      </c>
+      <c r="C439" t="s">
+        <v>236</v>
+      </c>
+      <c r="D439" t="s">
+        <v>31</v>
+      </c>
+      <c r="E439" t="s">
+        <v>32</v>
+      </c>
+      <c r="F439" t="s">
+        <v>38</v>
+      </c>
+      <c r="G439" t="s">
+        <v>34</v>
+      </c>
+      <c r="H439" t="s">
+        <v>35</v>
+      </c>
+      <c r="I439">
+        <v>4</v>
+      </c>
+      <c r="J439" t="s">
+        <v>39</v>
+      </c>
+      <c r="K439">
+        <v>270</v>
+      </c>
+      <c r="L439">
+        <v>1.0925929999999999</v>
+      </c>
+      <c r="M439">
+        <v>57.5</v>
+      </c>
+      <c r="N439" t="s">
+        <v>52</v>
+      </c>
+      <c r="O439">
+        <v>0</v>
+      </c>
+      <c r="P439">
+        <v>230</v>
+      </c>
+      <c r="Q439" t="s">
+        <v>235</v>
+      </c>
+      <c r="R439">
+        <v>295</v>
+      </c>
+      <c r="S439">
+        <v>779.66101700000002</v>
+      </c>
+      <c r="T439">
+        <v>4</v>
+      </c>
+      <c r="V439">
+        <v>57.5</v>
+      </c>
+      <c r="W439">
+        <v>1.3559319999999999</v>
+      </c>
+      <c r="X439">
+        <v>4</v>
+      </c>
+      <c r="Y439">
+        <v>1.3559319999999999</v>
+      </c>
+      <c r="Z439">
+        <v>57.5</v>
+      </c>
+      <c r="AA439">
+        <v>1</v>
+      </c>
+      <c r="AB439">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="440" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A440" t="s">
+        <v>28</v>
+      </c>
+      <c r="B440" t="s">
+        <v>29</v>
+      </c>
+      <c r="C440" t="s">
+        <v>236</v>
+      </c>
+      <c r="D440" t="s">
+        <v>31</v>
+      </c>
+      <c r="E440" t="s">
+        <v>41</v>
+      </c>
+      <c r="F440" t="s">
+        <v>38</v>
+      </c>
+      <c r="G440" t="s">
+        <v>34</v>
+      </c>
+      <c r="H440" t="s">
+        <v>35</v>
+      </c>
+      <c r="I440">
+        <v>2</v>
+      </c>
+      <c r="J440" t="s">
+        <v>39</v>
+      </c>
+      <c r="K440">
+        <v>81</v>
+      </c>
+      <c r="L440">
+        <v>1.0864199999999999</v>
+      </c>
+      <c r="M440">
+        <v>55.5</v>
+      </c>
+      <c r="N440" t="s">
+        <v>52</v>
+      </c>
+      <c r="O440">
+        <v>0</v>
+      </c>
+      <c r="P440">
+        <v>111</v>
+      </c>
+      <c r="Q440" t="s">
+        <v>235</v>
+      </c>
+      <c r="R440">
+        <v>88</v>
+      </c>
+      <c r="S440">
+        <v>1261.363636</v>
+      </c>
+      <c r="T440">
+        <v>2</v>
+      </c>
+      <c r="V440">
+        <v>55.5</v>
+      </c>
+      <c r="W440">
+        <v>2.2727270000000002</v>
+      </c>
+      <c r="X440">
+        <v>2</v>
+      </c>
+      <c r="Y440">
+        <v>2.2727270000000002</v>
+      </c>
+      <c r="Z440">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="441" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A441" t="s">
+        <v>28</v>
+      </c>
+      <c r="B441" t="s">
+        <v>29</v>
+      </c>
+      <c r="C441" t="s">
+        <v>236</v>
+      </c>
+      <c r="D441" t="s">
+        <v>31</v>
+      </c>
+      <c r="E441" t="s">
+        <v>42</v>
+      </c>
+      <c r="F441" t="s">
+        <v>38</v>
+      </c>
+      <c r="G441" t="s">
+        <v>34</v>
+      </c>
+      <c r="H441" t="s">
+        <v>35</v>
+      </c>
+      <c r="I441">
+        <v>59</v>
+      </c>
+      <c r="J441" t="s">
+        <v>39</v>
+      </c>
+      <c r="K441">
+        <v>795</v>
+      </c>
+      <c r="L441">
+        <v>1.108176</v>
+      </c>
+      <c r="M441">
+        <v>38.593220340000002</v>
+      </c>
+      <c r="N441" t="s">
+        <v>52</v>
+      </c>
+      <c r="O441">
+        <v>0</v>
+      </c>
+      <c r="P441">
+        <v>2277</v>
+      </c>
+      <c r="Q441" t="s">
+        <v>235</v>
+      </c>
+      <c r="R441">
+        <v>881</v>
+      </c>
+      <c r="S441">
+        <v>2584.562997</v>
+      </c>
+      <c r="T441">
+        <v>59</v>
+      </c>
+      <c r="V441">
+        <v>38.593220000000002</v>
+      </c>
+      <c r="W441">
+        <v>6.6969349999999999</v>
+      </c>
+      <c r="X441">
+        <v>62</v>
+      </c>
+      <c r="Y441">
+        <v>7.0374569999999999</v>
+      </c>
+      <c r="Z441">
+        <v>36.725805999999999</v>
+      </c>
+    </row>
+    <row r="442" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A442" t="s">
+        <v>28</v>
+      </c>
+      <c r="B442" t="s">
+        <v>29</v>
+      </c>
+      <c r="C442" t="s">
+        <v>234</v>
+      </c>
+      <c r="D442" t="s">
+        <v>31</v>
+      </c>
+      <c r="E442" t="s">
+        <v>32</v>
+      </c>
+      <c r="F442" t="s">
+        <v>38</v>
+      </c>
+      <c r="G442" t="s">
+        <v>34</v>
+      </c>
+      <c r="H442" t="s">
+        <v>35</v>
+      </c>
+      <c r="I442">
+        <v>16</v>
+      </c>
+      <c r="J442" t="s">
+        <v>39</v>
+      </c>
+      <c r="K442">
+        <v>1005</v>
+      </c>
+      <c r="L442">
+        <v>1.4537310000000001</v>
+      </c>
+      <c r="M442">
+        <v>49.6875</v>
+      </c>
+      <c r="N442" t="s">
+        <v>52</v>
+      </c>
+      <c r="O442">
+        <v>0</v>
+      </c>
+      <c r="P442">
+        <v>795</v>
+      </c>
+      <c r="Q442" t="s">
+        <v>233</v>
+      </c>
+      <c r="R442">
+        <v>1461</v>
+      </c>
+      <c r="S442">
+        <v>544.14784399999996</v>
+      </c>
+      <c r="T442">
+        <v>16</v>
+      </c>
+      <c r="V442">
+        <v>49.6875</v>
+      </c>
+      <c r="W442">
+        <v>1.09514</v>
+      </c>
+      <c r="X442">
+        <v>17</v>
+      </c>
+      <c r="Y442">
+        <v>1.1635869999999999</v>
+      </c>
+      <c r="Z442">
+        <v>46.764705999999997</v>
+      </c>
+      <c r="AA442">
+        <v>6</v>
+      </c>
+      <c r="AB442">
+        <v>132.5</v>
+      </c>
+    </row>
+    <row r="443" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A443" t="s">
+        <v>28</v>
+      </c>
+      <c r="B443" t="s">
+        <v>29</v>
+      </c>
+      <c r="C443" t="s">
+        <v>234</v>
+      </c>
+      <c r="D443" t="s">
+        <v>31</v>
+      </c>
+      <c r="E443" t="s">
+        <v>40</v>
+      </c>
+      <c r="F443" t="s">
+        <v>38</v>
+      </c>
+      <c r="G443" t="s">
+        <v>34</v>
+      </c>
+      <c r="H443" t="s">
+        <v>35</v>
+      </c>
+      <c r="K443">
+        <v>1</v>
+      </c>
+      <c r="L443">
+        <v>1</v>
+      </c>
+      <c r="N443" t="s">
+        <v>52</v>
+      </c>
+      <c r="O443">
+        <v>0</v>
+      </c>
+      <c r="P443">
+        <v>1</v>
+      </c>
+      <c r="Q443" t="s">
+        <v>233</v>
+      </c>
+      <c r="R443">
+        <v>1</v>
+      </c>
+      <c r="S443">
+        <v>1000</v>
+      </c>
+      <c r="X443">
+        <v>0</v>
+      </c>
+      <c r="Y443">
+        <v>0</v>
+      </c>
+      <c r="Z443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A444" t="s">
+        <v>28</v>
+      </c>
+      <c r="B444" t="s">
+        <v>29</v>
+      </c>
+      <c r="C444" t="s">
+        <v>234</v>
+      </c>
+      <c r="D444" t="s">
+        <v>31</v>
+      </c>
+      <c r="E444" t="s">
+        <v>41</v>
+      </c>
+      <c r="F444" t="s">
+        <v>38</v>
+      </c>
+      <c r="G444" t="s">
+        <v>34</v>
+      </c>
+      <c r="H444" t="s">
+        <v>35</v>
+      </c>
+      <c r="I444">
+        <v>1</v>
+      </c>
+      <c r="J444" t="s">
+        <v>39</v>
+      </c>
+      <c r="K444">
+        <v>35</v>
+      </c>
+      <c r="L444">
+        <v>1.3142860000000001</v>
+      </c>
+      <c r="M444">
+        <v>32</v>
+      </c>
+      <c r="N444" t="s">
+        <v>52</v>
+      </c>
+      <c r="O444">
+        <v>0</v>
+      </c>
+      <c r="P444">
+        <v>32</v>
+      </c>
+      <c r="Q444" t="s">
+        <v>233</v>
+      </c>
+      <c r="R444">
+        <v>46</v>
+      </c>
+      <c r="S444">
+        <v>695.65217399999995</v>
+      </c>
+      <c r="T444">
+        <v>1</v>
+      </c>
+      <c r="V444">
+        <v>32</v>
+      </c>
+      <c r="W444">
+        <v>2.1739130000000002</v>
+      </c>
+      <c r="X444">
+        <v>1</v>
+      </c>
+      <c r="Y444">
+        <v>2.1739130000000002</v>
+      </c>
+      <c r="Z444">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="445" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A445" t="s">
+        <v>28</v>
+      </c>
+      <c r="B445" t="s">
+        <v>29</v>
+      </c>
+      <c r="C445" t="s">
+        <v>234</v>
+      </c>
+      <c r="D445" t="s">
+        <v>31</v>
+      </c>
+      <c r="E445" t="s">
+        <v>42</v>
+      </c>
+      <c r="F445" t="s">
+        <v>38</v>
+      </c>
+      <c r="G445" t="s">
+        <v>34</v>
+      </c>
+      <c r="H445" t="s">
+        <v>35</v>
+      </c>
+      <c r="I445">
+        <v>45</v>
+      </c>
+      <c r="J445" t="s">
+        <v>39</v>
+      </c>
+      <c r="K445">
+        <v>2055</v>
+      </c>
+      <c r="L445">
+        <v>1.130414</v>
+      </c>
+      <c r="M445">
+        <v>58.311111109999999</v>
+      </c>
+      <c r="N445" t="s">
+        <v>52</v>
+      </c>
+      <c r="O445">
+        <v>0</v>
+      </c>
+      <c r="P445">
+        <v>2624</v>
+      </c>
+      <c r="Q445" t="s">
+        <v>233</v>
+      </c>
+      <c r="R445">
+        <v>2323</v>
+      </c>
+      <c r="S445">
+        <v>1129.5738269999999</v>
+      </c>
+      <c r="T445">
+        <v>45</v>
+      </c>
+      <c r="V445">
+        <v>58.311110999999997</v>
+      </c>
+      <c r="W445">
+        <v>1.9371499999999999</v>
+      </c>
+      <c r="X445">
+        <v>46</v>
+      </c>
+      <c r="Y445">
+        <v>1.9801979999999999</v>
+      </c>
+      <c r="Z445">
+        <v>57.043478</v>
+      </c>
+      <c r="AA445">
+        <v>22</v>
+      </c>
+      <c r="AB445">
+        <v>119.272727</v>
+      </c>
+    </row>
+    <row r="446" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A446" t="s">
+        <v>28</v>
+      </c>
+      <c r="B446" t="s">
+        <v>29</v>
+      </c>
+      <c r="C446" t="s">
+        <v>232</v>
+      </c>
+      <c r="D446" t="s">
+        <v>31</v>
+      </c>
+      <c r="E446" t="s">
+        <v>32</v>
+      </c>
+      <c r="F446" t="s">
+        <v>38</v>
+      </c>
+      <c r="G446" t="s">
+        <v>34</v>
+      </c>
+      <c r="H446" t="s">
+        <v>35</v>
+      </c>
+      <c r="I446">
+        <v>91</v>
+      </c>
+      <c r="J446" t="s">
+        <v>39</v>
+      </c>
+      <c r="K446">
+        <v>2741</v>
+      </c>
+      <c r="L446">
+        <v>1.238964</v>
+      </c>
+      <c r="M446">
+        <v>22.934065929999999</v>
+      </c>
+      <c r="N446" t="s">
+        <v>52</v>
+      </c>
+      <c r="O446">
+        <v>0</v>
+      </c>
+      <c r="P446">
+        <v>2087</v>
+      </c>
+      <c r="Q446" t="s">
+        <v>231</v>
+      </c>
+      <c r="R446">
+        <v>3396</v>
+      </c>
+      <c r="S446">
+        <v>614.54652499999997</v>
+      </c>
+      <c r="T446">
+        <v>91</v>
+      </c>
+      <c r="V446">
+        <v>22.934066000000001</v>
+      </c>
+      <c r="W446">
+        <v>2.6796229999999999</v>
+      </c>
+      <c r="X446">
+        <v>94</v>
+      </c>
+      <c r="Y446">
+        <v>2.7679619999999998</v>
+      </c>
+      <c r="Z446">
+        <v>22.202127999999998</v>
+      </c>
+      <c r="AA446">
+        <v>61</v>
+      </c>
+      <c r="AB446">
+        <v>34.213115000000002</v>
+      </c>
+    </row>
+    <row r="447" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A447" t="s">
+        <v>28</v>
+      </c>
+      <c r="B447" t="s">
+        <v>29</v>
+      </c>
+      <c r="C447" t="s">
+        <v>232</v>
+      </c>
+      <c r="D447" t="s">
+        <v>31</v>
+      </c>
+      <c r="E447" t="s">
+        <v>41</v>
+      </c>
+      <c r="F447" t="s">
+        <v>38</v>
+      </c>
+      <c r="G447" t="s">
+        <v>34</v>
+      </c>
+      <c r="H447" t="s">
+        <v>35</v>
+      </c>
+      <c r="I447">
+        <v>46</v>
+      </c>
+      <c r="J447" t="s">
+        <v>39</v>
+      </c>
+      <c r="K447">
+        <v>937</v>
+      </c>
+      <c r="L447">
+        <v>1.223052</v>
+      </c>
+      <c r="M447">
+        <v>24.195652169999999</v>
+      </c>
+      <c r="N447" t="s">
+        <v>52</v>
+      </c>
+      <c r="O447">
+        <v>0</v>
+      </c>
+      <c r="P447">
+        <v>1113</v>
+      </c>
+      <c r="Q447" t="s">
+        <v>231</v>
+      </c>
+      <c r="R447">
+        <v>1146</v>
+      </c>
+      <c r="S447">
+        <v>971.20418800000004</v>
+      </c>
+      <c r="T447">
+        <v>46</v>
+      </c>
+      <c r="V447">
+        <v>24.195651999999999</v>
+      </c>
+      <c r="W447">
+        <v>4.0139620000000003</v>
+      </c>
+      <c r="X447">
+        <v>55</v>
+      </c>
+      <c r="Y447">
+        <v>4.799302</v>
+      </c>
+      <c r="Z447">
+        <v>20.236363999999998</v>
+      </c>
+      <c r="AA447">
+        <v>38</v>
+      </c>
+      <c r="AB447">
+        <v>29.289473999999998</v>
+      </c>
+    </row>
+    <row r="448" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A448" t="s">
+        <v>28</v>
+      </c>
+      <c r="B448" t="s">
+        <v>29</v>
+      </c>
+      <c r="C448" t="s">
+        <v>232</v>
+      </c>
+      <c r="D448" t="s">
+        <v>31</v>
+      </c>
+      <c r="E448" t="s">
+        <v>42</v>
+      </c>
+      <c r="F448" t="s">
+        <v>38</v>
+      </c>
+      <c r="G448" t="s">
+        <v>34</v>
+      </c>
+      <c r="H448" t="s">
+        <v>35</v>
+      </c>
+      <c r="I448">
+        <v>18</v>
+      </c>
+      <c r="J448" t="s">
+        <v>39</v>
+      </c>
+      <c r="K448">
+        <v>354</v>
+      </c>
+      <c r="L448">
+        <v>1.0734459999999999</v>
+      </c>
+      <c r="M448">
+        <v>38.666666669999998</v>
+      </c>
+      <c r="N448" t="s">
+        <v>52</v>
+      </c>
+      <c r="O448">
+        <v>0</v>
+      </c>
+      <c r="P448">
+        <v>696</v>
+      </c>
+      <c r="Q448" t="s">
+        <v>231</v>
+      </c>
+      <c r="R448">
+        <v>380</v>
+      </c>
+      <c r="S448">
+        <v>1831.578947</v>
+      </c>
+      <c r="T448">
+        <v>18</v>
+      </c>
+      <c r="V448">
+        <v>38.666666999999997</v>
+      </c>
+      <c r="W448">
+        <v>4.7368420000000002</v>
+      </c>
+      <c r="X448">
+        <v>20</v>
+      </c>
+      <c r="Y448">
+        <v>5.2631579999999998</v>
+      </c>
+      <c r="Z448">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="AA448">
+        <v>15</v>
+      </c>
+      <c r="AB448">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="449" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A449" t="s">
+        <v>28</v>
+      </c>
+      <c r="B449" t="s">
+        <v>29</v>
+      </c>
+      <c r="C449" t="s">
+        <v>230</v>
+      </c>
+      <c r="D449" t="s">
+        <v>31</v>
+      </c>
+      <c r="E449" t="s">
+        <v>32</v>
+      </c>
+      <c r="F449" t="s">
+        <v>38</v>
+      </c>
+      <c r="G449" t="s">
+        <v>34</v>
+      </c>
+      <c r="H449" t="s">
+        <v>35</v>
+      </c>
+      <c r="I449">
+        <v>8</v>
+      </c>
+      <c r="J449" t="s">
+        <v>39</v>
+      </c>
+      <c r="K449">
+        <v>408</v>
+      </c>
+      <c r="L449">
+        <v>1.156863</v>
+      </c>
+      <c r="M449">
+        <v>48.5</v>
+      </c>
+      <c r="N449" t="s">
+        <v>52</v>
+      </c>
+      <c r="O449">
+        <v>0</v>
+      </c>
+      <c r="P449">
+        <v>388</v>
+      </c>
+      <c r="Q449" t="s">
+        <v>228</v>
+      </c>
+      <c r="R449">
+        <v>472</v>
+      </c>
+      <c r="S449">
+        <v>822.03389800000002</v>
+      </c>
+      <c r="T449">
+        <v>8</v>
+      </c>
+      <c r="V449">
+        <v>48.5</v>
+      </c>
+      <c r="W449">
+        <v>1.6949149999999999</v>
+      </c>
+      <c r="X449">
+        <v>9</v>
+      </c>
+      <c r="Y449">
+        <v>1.9067799999999999</v>
+      </c>
+      <c r="Z449">
+        <v>43.111111000000001</v>
+      </c>
+      <c r="AA449">
+        <v>6</v>
+      </c>
+      <c r="AB449">
+        <v>64.666667000000004</v>
+      </c>
+    </row>
+    <row r="450" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A450" t="s">
+        <v>28</v>
+      </c>
+      <c r="B450" t="s">
+        <v>29</v>
+      </c>
+      <c r="C450" t="s">
+        <v>230</v>
+      </c>
+      <c r="D450" t="s">
+        <v>31</v>
+      </c>
+      <c r="E450" t="s">
+        <v>40</v>
+      </c>
+      <c r="F450" t="s">
+        <v>38</v>
+      </c>
+      <c r="G450" t="s">
+        <v>34</v>
+      </c>
+      <c r="H450" t="s">
+        <v>35</v>
+      </c>
+      <c r="K450">
+        <v>1</v>
+      </c>
+      <c r="L450">
+        <v>1</v>
+      </c>
+      <c r="N450" t="s">
+        <v>52</v>
+      </c>
+      <c r="O450">
+        <v>0</v>
+      </c>
+      <c r="P450">
+        <v>0</v>
+      </c>
+      <c r="Q450" t="s">
+        <v>228</v>
+      </c>
+      <c r="R450">
+        <v>1</v>
+      </c>
+      <c r="S450">
+        <v>0</v>
+      </c>
+      <c r="X450">
+        <v>0</v>
+      </c>
+      <c r="Y450">
+        <v>0</v>
+      </c>
+      <c r="Z450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A451" t="s">
+        <v>28</v>
+      </c>
+      <c r="B451" t="s">
+        <v>29</v>
+      </c>
+      <c r="C451" t="s">
+        <v>230</v>
+      </c>
+      <c r="D451" t="s">
+        <v>31</v>
+      </c>
+      <c r="E451" t="s">
+        <v>41</v>
+      </c>
+      <c r="F451" t="s">
+        <v>38</v>
+      </c>
+      <c r="G451" t="s">
+        <v>34</v>
+      </c>
+      <c r="H451" t="s">
+        <v>35</v>
+      </c>
+      <c r="I451">
+        <v>5</v>
+      </c>
+      <c r="J451" t="s">
+        <v>39</v>
+      </c>
+      <c r="K451">
+        <v>181</v>
+      </c>
+      <c r="L451">
+        <v>1.1325970000000001</v>
+      </c>
+      <c r="M451">
+        <v>38.6</v>
+      </c>
+      <c r="N451" t="s">
+        <v>52</v>
+      </c>
+      <c r="O451">
+        <v>0</v>
+      </c>
+      <c r="P451">
+        <v>193</v>
+      </c>
+      <c r="Q451" t="s">
+        <v>228</v>
+      </c>
+      <c r="R451">
+        <v>205</v>
+      </c>
+      <c r="S451">
+        <v>941.46341500000005</v>
+      </c>
+      <c r="T451">
+        <v>5</v>
+      </c>
+      <c r="V451">
+        <v>38.6</v>
+      </c>
+      <c r="W451">
+        <v>2.4390239999999999</v>
+      </c>
+      <c r="X451">
+        <v>8</v>
+      </c>
+      <c r="Y451">
+        <v>3.9024390000000002</v>
+      </c>
+      <c r="Z451">
+        <v>24.125</v>
+      </c>
+      <c r="AA451">
+        <v>4</v>
+      </c>
+      <c r="AB451">
+        <v>48.25</v>
+      </c>
+    </row>
+    <row r="452" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A452" t="s">
+        <v>28</v>
+      </c>
+      <c r="B452" t="s">
+        <v>29</v>
+      </c>
+      <c r="C452" t="s">
+        <v>230</v>
+      </c>
+      <c r="D452" t="s">
+        <v>31</v>
+      </c>
+      <c r="E452" t="s">
+        <v>42</v>
+      </c>
+      <c r="F452" t="s">
+        <v>38</v>
+      </c>
+      <c r="G452" t="s">
+        <v>34</v>
+      </c>
+      <c r="H452" t="s">
+        <v>35</v>
+      </c>
+      <c r="I452">
+        <v>89</v>
+      </c>
+      <c r="J452" t="s">
+        <v>39</v>
+      </c>
+      <c r="K452">
+        <v>2707</v>
+      </c>
+      <c r="L452">
+        <v>1.2053929999999999</v>
+      </c>
+      <c r="M452">
+        <v>42.797752809999999</v>
+      </c>
+      <c r="N452" t="s">
+        <v>52</v>
+      </c>
+      <c r="O452">
+        <v>0</v>
+      </c>
+      <c r="P452">
+        <v>3809</v>
+      </c>
+      <c r="Q452" t="s">
+        <v>228</v>
+      </c>
+      <c r="R452">
+        <v>3263</v>
+      </c>
+      <c r="S452">
+        <v>1167.3306769999999</v>
+      </c>
+      <c r="T452">
+        <v>89</v>
+      </c>
+      <c r="V452">
+        <v>42.797753</v>
+      </c>
+      <c r="W452">
+        <v>2.7275510000000001</v>
+      </c>
+      <c r="X452">
+        <v>99</v>
+      </c>
+      <c r="Y452">
+        <v>3.0340180000000001</v>
+      </c>
+      <c r="Z452">
+        <v>38.474747000000001</v>
+      </c>
+      <c r="AA452">
+        <v>70</v>
+      </c>
+      <c r="AB452">
+        <v>54.414285999999997</v>
+      </c>
+    </row>
+    <row r="453" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A453" t="s">
+        <v>28</v>
+      </c>
+      <c r="B453" t="s">
+        <v>29</v>
+      </c>
+      <c r="C453" t="s">
+        <v>230</v>
+      </c>
+      <c r="D453" t="s">
+        <v>31</v>
+      </c>
+      <c r="E453" t="s">
+        <v>42</v>
+      </c>
+      <c r="F453" t="s">
+        <v>229</v>
+      </c>
+      <c r="G453" t="s">
+        <v>34</v>
+      </c>
+      <c r="H453" t="s">
+        <v>35</v>
+      </c>
+      <c r="K453">
+        <v>1</v>
+      </c>
+      <c r="L453">
+        <v>1</v>
+      </c>
+      <c r="N453" t="s">
+        <v>52</v>
+      </c>
+      <c r="O453">
+        <v>0</v>
+      </c>
+      <c r="P453">
+        <v>2</v>
+      </c>
+      <c r="Q453" t="s">
+        <v>228</v>
+      </c>
+      <c r="R453">
+        <v>1</v>
+      </c>
+      <c r="S453">
+        <v>2000</v>
+      </c>
+      <c r="X453">
+        <v>0</v>
+      </c>
+      <c r="Y453">
+        <v>0</v>
+      </c>
+      <c r="Z453">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A454" t="s">
+        <v>28</v>
+      </c>
+      <c r="B454" t="s">
+        <v>29</v>
+      </c>
+      <c r="C454" t="s">
+        <v>227</v>
+      </c>
+      <c r="D454" t="s">
+        <v>31</v>
+      </c>
+      <c r="E454" t="s">
+        <v>32</v>
+      </c>
+      <c r="F454" t="s">
+        <v>38</v>
+      </c>
+      <c r="G454" t="s">
+        <v>34</v>
+      </c>
+      <c r="H454" t="s">
+        <v>35</v>
+      </c>
+      <c r="I454">
+        <v>7</v>
+      </c>
+      <c r="J454" t="s">
+        <v>51</v>
+      </c>
+      <c r="K454">
+        <v>300</v>
+      </c>
+      <c r="L454">
+        <v>1.243333</v>
+      </c>
+      <c r="M454">
+        <v>65.571428569999995</v>
+      </c>
+      <c r="N454" t="s">
+        <v>52</v>
+      </c>
+      <c r="O454">
+        <v>0</v>
+      </c>
+      <c r="P454">
+        <v>459</v>
+      </c>
+      <c r="Q454" t="s">
+        <v>226</v>
+      </c>
+      <c r="R454">
+        <v>373</v>
+      </c>
+      <c r="S454">
+        <v>1230.563003</v>
+      </c>
+      <c r="T454">
+        <v>7</v>
+      </c>
+      <c r="V454">
+        <v>65.571428999999995</v>
+      </c>
+      <c r="W454">
+        <v>1.876676</v>
+      </c>
+      <c r="X454">
+        <v>12</v>
+      </c>
+      <c r="Y454">
+        <v>3.217158</v>
+      </c>
+      <c r="Z454">
+        <v>38.25</v>
+      </c>
+      <c r="AA454">
+        <v>7</v>
+      </c>
+      <c r="AB454">
+        <v>65.571428999999995</v>
+      </c>
+    </row>
+    <row r="455" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A455" t="s">
+        <v>28</v>
+      </c>
+      <c r="B455" t="s">
+        <v>29</v>
+      </c>
+      <c r="C455" t="s">
+        <v>227</v>
+      </c>
+      <c r="D455" t="s">
+        <v>31</v>
+      </c>
+      <c r="E455" t="s">
+        <v>41</v>
+      </c>
+      <c r="F455" t="s">
+        <v>38</v>
+      </c>
+      <c r="G455" t="s">
+        <v>34</v>
+      </c>
+      <c r="H455" t="s">
+        <v>35</v>
+      </c>
+      <c r="I455">
+        <v>9</v>
+      </c>
+      <c r="J455" t="s">
+        <v>51</v>
+      </c>
+      <c r="K455">
+        <v>195</v>
+      </c>
+      <c r="L455">
+        <v>1.235897</v>
+      </c>
+      <c r="M455">
+        <v>33.444444439999998</v>
+      </c>
+      <c r="N455" t="s">
+        <v>52</v>
+      </c>
+      <c r="O455">
+        <v>0</v>
+      </c>
+      <c r="P455">
+        <v>301</v>
+      </c>
+      <c r="Q455" t="s">
+        <v>226</v>
+      </c>
+      <c r="R455">
+        <v>241</v>
+      </c>
+      <c r="S455">
+        <v>1248.9626559999999</v>
+      </c>
+      <c r="T455">
+        <v>9</v>
+      </c>
+      <c r="V455">
+        <v>33.444443999999997</v>
+      </c>
+      <c r="W455">
+        <v>3.7344400000000002</v>
+      </c>
+      <c r="X455">
+        <v>15</v>
+      </c>
+      <c r="Y455">
+        <v>6.2240659999999997</v>
+      </c>
+      <c r="Z455">
+        <v>20.066666999999999</v>
+      </c>
+      <c r="AA455">
+        <v>9</v>
+      </c>
+      <c r="AB455">
+        <v>33.444443999999997</v>
+      </c>
+    </row>
+    <row r="456" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A456" t="s">
+        <v>28</v>
+      </c>
+      <c r="B456" t="s">
+        <v>29</v>
+      </c>
+      <c r="C456" t="s">
+        <v>227</v>
+      </c>
+      <c r="D456" t="s">
+        <v>31</v>
+      </c>
+      <c r="E456" t="s">
+        <v>42</v>
+      </c>
+      <c r="F456" t="s">
+        <v>38</v>
+      </c>
+      <c r="G456" t="s">
+        <v>34</v>
+      </c>
+      <c r="H456" t="s">
+        <v>35</v>
+      </c>
+      <c r="I456">
+        <v>65</v>
+      </c>
+      <c r="J456" t="s">
+        <v>51</v>
+      </c>
+      <c r="K456">
+        <v>2904</v>
+      </c>
+      <c r="L456">
+        <v>1.28478</v>
+      </c>
+      <c r="M456">
+        <v>58.323076919999998</v>
+      </c>
+      <c r="N456" t="s">
+        <v>52</v>
+      </c>
+      <c r="O456">
+        <v>0</v>
+      </c>
+      <c r="P456">
+        <v>3791</v>
+      </c>
+      <c r="Q456" t="s">
+        <v>226</v>
+      </c>
+      <c r="R456">
+        <v>3731</v>
+      </c>
+      <c r="S456">
+        <v>1016.0814800000001</v>
+      </c>
+      <c r="T456">
+        <v>98</v>
+      </c>
+      <c r="V456">
+        <v>38.683672999999999</v>
+      </c>
+      <c r="W456">
+        <v>2.6266419999999999</v>
+      </c>
+      <c r="X456">
+        <v>103</v>
+      </c>
+      <c r="Y456">
+        <v>2.7606540000000002</v>
+      </c>
+      <c r="Z456">
+        <v>36.805824999999999</v>
+      </c>
+      <c r="AA456">
+        <v>65</v>
+      </c>
+      <c r="AB456">
+        <v>58.323076999999998</v>
+      </c>
+    </row>
+    <row r="457" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A457" t="s">
+        <v>28</v>
+      </c>
+      <c r="B457" t="s">
+        <v>29</v>
+      </c>
+      <c r="C457" t="s">
+        <v>225</v>
+      </c>
+      <c r="D457" t="s">
+        <v>31</v>
+      </c>
+      <c r="E457" t="s">
+        <v>32</v>
+      </c>
+      <c r="F457" t="s">
+        <v>38</v>
+      </c>
+      <c r="G457" t="s">
+        <v>34</v>
+      </c>
+      <c r="H457" t="s">
+        <v>35</v>
+      </c>
+      <c r="I457">
+        <v>12</v>
+      </c>
+      <c r="J457" t="s">
+        <v>51</v>
+      </c>
+      <c r="K457">
+        <v>559</v>
+      </c>
+      <c r="L457">
+        <v>1.223614</v>
+      </c>
+      <c r="M457">
+        <v>40.416666669999998</v>
+      </c>
+      <c r="N457" t="s">
+        <v>52</v>
+      </c>
+      <c r="O457">
+        <v>0</v>
+      </c>
+      <c r="P457">
+        <v>485</v>
+      </c>
+      <c r="Q457" t="s">
+        <v>68</v>
+      </c>
+      <c r="R457">
+        <v>684</v>
+      </c>
+      <c r="S457">
+        <v>709.06432700000005</v>
+      </c>
+      <c r="T457">
+        <v>17</v>
+      </c>
+      <c r="V457">
+        <v>28.529412000000001</v>
+      </c>
+      <c r="W457">
+        <v>2.4853800000000001</v>
+      </c>
+      <c r="X457">
+        <v>19</v>
+      </c>
+      <c r="Y457">
+        <v>2.7777780000000001</v>
+      </c>
+      <c r="Z457">
+        <v>25.526316000000001</v>
+      </c>
+      <c r="AA457">
+        <v>12</v>
+      </c>
+      <c r="AB457">
+        <v>40.416666999999997</v>
+      </c>
+    </row>
+    <row r="458" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A458" t="s">
+        <v>28</v>
+      </c>
+      <c r="B458" t="s">
+        <v>29</v>
+      </c>
+      <c r="C458" t="s">
+        <v>225</v>
+      </c>
+      <c r="D458" t="s">
+        <v>31</v>
+      </c>
+      <c r="E458" t="s">
+        <v>41</v>
+      </c>
+      <c r="F458" t="s">
+        <v>38</v>
+      </c>
+      <c r="G458" t="s">
+        <v>34</v>
+      </c>
+      <c r="H458" t="s">
+        <v>35</v>
+      </c>
+      <c r="I458">
+        <v>8</v>
+      </c>
+      <c r="J458" t="s">
+        <v>51</v>
+      </c>
+      <c r="K458">
+        <v>247</v>
+      </c>
+      <c r="L458">
+        <v>1.255061</v>
+      </c>
+      <c r="M458">
+        <v>35.625</v>
+      </c>
+      <c r="N458" t="s">
+        <v>52</v>
+      </c>
+      <c r="O458">
+        <v>0</v>
+      </c>
+      <c r="P458">
+        <v>285</v>
+      </c>
+      <c r="Q458" t="s">
+        <v>68</v>
+      </c>
+      <c r="R458">
+        <v>310</v>
+      </c>
+      <c r="S458">
+        <v>919.35483899999997</v>
+      </c>
+      <c r="T458">
+        <v>8</v>
+      </c>
+      <c r="V458">
+        <v>35.625</v>
+      </c>
+      <c r="W458">
+        <v>2.5806450000000001</v>
+      </c>
+      <c r="X458">
+        <v>9</v>
+      </c>
+      <c r="Y458">
+        <v>2.9032260000000001</v>
+      </c>
+      <c r="Z458">
+        <v>31.666667</v>
+      </c>
+      <c r="AA458">
+        <v>8</v>
+      </c>
+      <c r="AB458">
+        <v>35.625</v>
+      </c>
+    </row>
+    <row r="459" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A459" t="s">
+        <v>28</v>
+      </c>
+      <c r="B459" t="s">
+        <v>29</v>
+      </c>
+      <c r="C459" t="s">
+        <v>225</v>
+      </c>
+      <c r="D459" t="s">
+        <v>31</v>
+      </c>
+      <c r="E459" t="s">
+        <v>42</v>
+      </c>
+      <c r="F459" t="s">
+        <v>38</v>
+      </c>
+      <c r="G459" t="s">
+        <v>34</v>
+      </c>
+      <c r="H459" t="s">
+        <v>35</v>
+      </c>
+      <c r="I459">
+        <v>89</v>
+      </c>
+      <c r="J459" t="s">
+        <v>51</v>
+      </c>
+      <c r="K459">
+        <v>2107</v>
+      </c>
+      <c r="L459">
+        <v>1.235406</v>
+      </c>
+      <c r="M459">
+        <v>43.617977529999997</v>
+      </c>
+      <c r="N459" t="s">
+        <v>52</v>
+      </c>
+      <c r="O459">
+        <v>0</v>
+      </c>
+      <c r="P459">
+        <v>3882</v>
+      </c>
+      <c r="Q459" t="s">
+        <v>68</v>
+      </c>
+      <c r="R459">
+        <v>2603</v>
+      </c>
+      <c r="S459">
+        <v>1491.3561279999999</v>
+      </c>
+      <c r="T459">
+        <v>96</v>
+      </c>
+      <c r="V459">
+        <v>40.4375</v>
+      </c>
+      <c r="W459">
+        <v>3.6880519999999999</v>
+      </c>
+      <c r="X459">
+        <v>105</v>
+      </c>
+      <c r="Y459">
+        <v>4.0338070000000004</v>
+      </c>
+      <c r="Z459">
+        <v>36.971429000000001</v>
+      </c>
+      <c r="AA459">
+        <v>89</v>
+      </c>
+      <c r="AB459">
+        <v>43.617978000000001</v>
+      </c>
+    </row>
+    <row r="460" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A460" t="s">
+        <v>28</v>
+      </c>
+      <c r="B460" t="s">
+        <v>29</v>
+      </c>
+      <c r="C460" t="s">
+        <v>224</v>
+      </c>
+      <c r="D460" t="s">
+        <v>31</v>
+      </c>
+      <c r="E460" t="s">
+        <v>32</v>
+      </c>
+      <c r="F460" t="s">
+        <v>38</v>
+      </c>
+      <c r="G460" t="s">
+        <v>216</v>
+      </c>
+      <c r="H460" t="s">
+        <v>35</v>
+      </c>
+      <c r="I460">
+        <v>3</v>
+      </c>
+      <c r="J460" t="s">
+        <v>51</v>
+      </c>
+      <c r="K460">
+        <v>113</v>
+      </c>
+      <c r="L460">
+        <v>1.0530969999999999</v>
+      </c>
+      <c r="M460">
+        <v>29.666666670000001</v>
+      </c>
+      <c r="N460" t="s">
+        <v>52</v>
+      </c>
+      <c r="O460">
+        <v>0</v>
+      </c>
+      <c r="P460">
+        <v>89</v>
+      </c>
+      <c r="Q460" t="s">
+        <v>223</v>
+      </c>
+      <c r="R460">
+        <v>119</v>
+      </c>
+      <c r="S460">
+        <v>747.89916000000005</v>
+      </c>
+      <c r="T460">
+        <v>4</v>
+      </c>
+      <c r="V460">
+        <v>22.25</v>
+      </c>
+      <c r="W460">
+        <v>3.361345</v>
+      </c>
+      <c r="X460">
+        <v>5</v>
+      </c>
+      <c r="Y460">
+        <v>4.2016809999999998</v>
+      </c>
+      <c r="Z460">
+        <v>17.8</v>
+      </c>
+      <c r="AA460">
+        <v>3</v>
+      </c>
+      <c r="AB460">
+        <v>29.666667</v>
+      </c>
+    </row>
+    <row r="461" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A461" t="s">
+        <v>28</v>
+      </c>
+      <c r="B461" t="s">
+        <v>29</v>
+      </c>
+      <c r="C461" t="s">
+        <v>224</v>
+      </c>
+      <c r="D461" t="s">
+        <v>31</v>
+      </c>
+      <c r="E461" t="s">
+        <v>40</v>
+      </c>
+      <c r="F461" t="s">
+        <v>38</v>
+      </c>
+      <c r="G461" t="s">
+        <v>216</v>
+      </c>
+      <c r="H461" t="s">
+        <v>35</v>
+      </c>
+      <c r="K461">
+        <v>1</v>
+      </c>
+      <c r="L461">
+        <v>1</v>
+      </c>
+      <c r="N461" t="s">
+        <v>52</v>
+      </c>
+      <c r="O461">
+        <v>0</v>
+      </c>
+      <c r="P461">
+        <v>1</v>
+      </c>
+      <c r="Q461" t="s">
+        <v>223</v>
+      </c>
+      <c r="R461">
+        <v>1</v>
+      </c>
+      <c r="S461">
+        <v>1000</v>
+      </c>
+      <c r="X461">
+        <v>0</v>
+      </c>
+      <c r="Y461">
+        <v>0</v>
+      </c>
+      <c r="Z461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A462" t="s">
+        <v>28</v>
+      </c>
+      <c r="B462" t="s">
+        <v>29</v>
+      </c>
+      <c r="C462" t="s">
+        <v>224</v>
+      </c>
+      <c r="D462" t="s">
+        <v>31</v>
+      </c>
+      <c r="E462" t="s">
+        <v>41</v>
+      </c>
+      <c r="F462" t="s">
+        <v>38</v>
+      </c>
+      <c r="G462" t="s">
+        <v>216</v>
+      </c>
+      <c r="H462" t="s">
+        <v>35</v>
+      </c>
+      <c r="I462">
+        <v>1</v>
+      </c>
+      <c r="J462" t="s">
+        <v>51</v>
+      </c>
+      <c r="K462">
+        <v>31</v>
+      </c>
+      <c r="L462">
+        <v>1</v>
+      </c>
+      <c r="M462">
+        <v>41</v>
+      </c>
+      <c r="N462" t="s">
+        <v>52</v>
+      </c>
+      <c r="O462">
+        <v>0</v>
+      </c>
+      <c r="P462">
+        <v>41</v>
+      </c>
+      <c r="Q462" t="s">
+        <v>223</v>
+      </c>
+      <c r="R462">
+        <v>31</v>
+      </c>
+      <c r="S462">
+        <v>1322.580645</v>
+      </c>
+      <c r="T462">
+        <v>1</v>
+      </c>
+      <c r="V462">
+        <v>41</v>
+      </c>
+      <c r="W462">
+        <v>3.225806</v>
+      </c>
+      <c r="X462">
+        <v>1</v>
+      </c>
+      <c r="Y462">
+        <v>3.225806</v>
+      </c>
+      <c r="Z462">
+        <v>41</v>
+      </c>
+      <c r="AA462">
+        <v>1</v>
+      </c>
+      <c r="AB462">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="463" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A463" t="s">
+        <v>28</v>
+      </c>
+      <c r="B463" t="s">
+        <v>29</v>
+      </c>
+      <c r="C463" t="s">
+        <v>224</v>
+      </c>
+      <c r="D463" t="s">
+        <v>31</v>
+      </c>
+      <c r="E463" t="s">
+        <v>42</v>
+      </c>
+      <c r="F463" t="s">
+        <v>38</v>
+      </c>
+      <c r="G463" t="s">
+        <v>216</v>
+      </c>
+      <c r="H463" t="s">
+        <v>35</v>
+      </c>
+      <c r="I463">
+        <v>36</v>
+      </c>
+      <c r="J463" t="s">
+        <v>51</v>
+      </c>
+      <c r="K463">
+        <v>583</v>
+      </c>
+      <c r="L463">
+        <v>1.034305</v>
+      </c>
+      <c r="M463">
+        <v>36.555555560000002</v>
+      </c>
+      <c r="N463" t="s">
+        <v>52</v>
+      </c>
+      <c r="O463">
+        <v>0</v>
+      </c>
+      <c r="P463">
+        <v>1316</v>
+      </c>
+      <c r="Q463" t="s">
+        <v>223</v>
+      </c>
+      <c r="R463">
+        <v>603</v>
+      </c>
+      <c r="S463">
+        <v>2182.4212269999998</v>
+      </c>
+      <c r="T463">
+        <v>39</v>
+      </c>
+      <c r="V463">
+        <v>33.743589999999998</v>
+      </c>
+      <c r="W463">
+        <v>6.4676619999999998</v>
+      </c>
+      <c r="X463">
+        <v>45</v>
+      </c>
+      <c r="Y463">
+        <v>7.4626869999999998</v>
+      </c>
+      <c r="Z463">
+        <v>29.244444000000001</v>
+      </c>
+      <c r="AA463">
+        <v>36</v>
+      </c>
+      <c r="AB463">
+        <v>36.555556000000003</v>
+      </c>
+    </row>
+    <row r="464" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A464" t="s">
+        <v>28</v>
+      </c>
+      <c r="B464" t="s">
+        <v>29</v>
+      </c>
+      <c r="C464" t="s">
+        <v>222</v>
+      </c>
+      <c r="D464" t="s">
+        <v>31</v>
+      </c>
+      <c r="E464" t="s">
+        <v>32</v>
+      </c>
+      <c r="F464" t="s">
+        <v>38</v>
+      </c>
+      <c r="G464" t="s">
+        <v>34</v>
+      </c>
+      <c r="H464" t="s">
+        <v>35</v>
+      </c>
+      <c r="I464">
+        <v>27</v>
+      </c>
+      <c r="J464" t="s">
+        <v>51</v>
+      </c>
+      <c r="K464">
+        <v>3975</v>
+      </c>
+      <c r="L464">
+        <v>1.502642</v>
+      </c>
+      <c r="M464">
+        <v>171.44444444000001</v>
+      </c>
+      <c r="N464" t="s">
+        <v>52</v>
+      </c>
+      <c r="O464">
+        <v>0</v>
+      </c>
+      <c r="P464">
+        <v>4629</v>
+      </c>
+      <c r="Q464" t="s">
+        <v>62</v>
+      </c>
+      <c r="R464">
+        <v>5973</v>
+      </c>
+      <c r="S464">
+        <v>774.98744399999998</v>
+      </c>
+      <c r="T464">
+        <v>54</v>
+      </c>
+      <c r="V464">
+        <v>85.722222000000002</v>
+      </c>
+      <c r="W464">
+        <v>0.90406799999999998</v>
+      </c>
+      <c r="X464">
+        <v>63</v>
+      </c>
+      <c r="Y464">
+        <v>1.054746</v>
+      </c>
+      <c r="Z464">
+        <v>73.476190000000003</v>
+      </c>
+      <c r="AA464">
+        <v>27</v>
+      </c>
+      <c r="AB464">
+        <v>171.444444</v>
+      </c>
+    </row>
+    <row r="465" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A465" t="s">
+        <v>28</v>
+      </c>
+      <c r="B465" t="s">
+        <v>29</v>
+      </c>
+      <c r="C465" t="s">
+        <v>222</v>
+      </c>
+      <c r="D465" t="s">
+        <v>31</v>
+      </c>
+      <c r="E465" t="s">
+        <v>41</v>
+      </c>
+      <c r="F465" t="s">
+        <v>38</v>
+      </c>
+      <c r="G465" t="s">
+        <v>34</v>
+      </c>
+      <c r="H465" t="s">
+        <v>35</v>
+      </c>
+      <c r="K465">
+        <v>1</v>
+      </c>
+      <c r="L465">
+        <v>1</v>
+      </c>
+      <c r="N465" t="s">
+        <v>52</v>
+      </c>
+      <c r="O465">
+        <v>0</v>
+      </c>
+      <c r="P465">
+        <v>1</v>
+      </c>
+      <c r="Q465" t="s">
+        <v>62</v>
+      </c>
+      <c r="R465">
+        <v>1</v>
+      </c>
+      <c r="S465">
+        <v>1000</v>
+      </c>
+      <c r="X465">
+        <v>0</v>
+      </c>
+      <c r="Y465">
+        <v>0</v>
+      </c>
+      <c r="Z465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A466" t="s">
+        <v>28</v>
+      </c>
+      <c r="B466" t="s">
+        <v>29</v>
+      </c>
+      <c r="C466" t="s">
+        <v>222</v>
+      </c>
+      <c r="D466" t="s">
+        <v>31</v>
+      </c>
+      <c r="E466" t="s">
+        <v>42</v>
+      </c>
+      <c r="F466" t="s">
+        <v>38</v>
+      </c>
+      <c r="G466" t="s">
+        <v>34</v>
+      </c>
+      <c r="H466" t="s">
+        <v>35</v>
+      </c>
+      <c r="K466">
+        <v>1</v>
+      </c>
+      <c r="L466">
+        <v>1</v>
+      </c>
+      <c r="N466" t="s">
+        <v>52</v>
+      </c>
+      <c r="O466">
+        <v>0</v>
+      </c>
+      <c r="P466">
+        <v>2</v>
+      </c>
+      <c r="Q466" t="s">
+        <v>62</v>
+      </c>
+      <c r="R466">
+        <v>1</v>
+      </c>
+      <c r="S466">
+        <v>2000</v>
+      </c>
+      <c r="X466">
+        <v>0</v>
+      </c>
+      <c r="Y466">
+        <v>0</v>
+      </c>
+      <c r="Z466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A467" t="s">
+        <v>28</v>
+      </c>
+      <c r="B467" t="s">
+        <v>29</v>
+      </c>
+      <c r="C467" t="s">
+        <v>221</v>
+      </c>
+      <c r="D467" t="s">
+        <v>31</v>
+      </c>
+      <c r="E467" t="s">
+        <v>32</v>
+      </c>
+      <c r="F467" t="s">
+        <v>38</v>
+      </c>
+      <c r="G467" t="s">
+        <v>34</v>
+      </c>
+      <c r="H467" t="s">
+        <v>35</v>
+      </c>
+      <c r="I467">
+        <v>110</v>
+      </c>
+      <c r="J467" t="s">
+        <v>51</v>
+      </c>
+      <c r="K467">
+        <v>3612</v>
+      </c>
+      <c r="L467">
+        <v>1.472315</v>
+      </c>
+      <c r="M467">
+        <v>53.718181819999998</v>
+      </c>
+      <c r="N467" t="s">
+        <v>52</v>
+      </c>
+      <c r="O467">
+        <v>0</v>
+      </c>
+      <c r="P467">
+        <v>5909</v>
+      </c>
+      <c r="Q467" t="s">
+        <v>220</v>
+      </c>
+      <c r="R467">
+        <v>5318</v>
+      </c>
+      <c r="S467">
+        <v>1111.1320049999999</v>
+      </c>
+      <c r="T467">
+        <v>141</v>
+      </c>
+      <c r="V467">
+        <v>41.907800999999999</v>
+      </c>
+      <c r="W467">
+        <v>2.651373</v>
+      </c>
+      <c r="X467">
+        <v>177</v>
+      </c>
+      <c r="Y467">
+        <v>3.328319</v>
+      </c>
+      <c r="Z467">
+        <v>33.384180999999998</v>
+      </c>
+      <c r="AA467">
+        <v>110</v>
+      </c>
+      <c r="AB467">
+        <v>53.718181999999999</v>
+      </c>
+    </row>
+    <row r="468" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A468" t="s">
+        <v>28</v>
+      </c>
+      <c r="B468" t="s">
+        <v>29</v>
+      </c>
+      <c r="C468" t="s">
+        <v>221</v>
+      </c>
+      <c r="D468" t="s">
+        <v>31</v>
+      </c>
+      <c r="E468" t="s">
+        <v>40</v>
+      </c>
+      <c r="F468" t="s">
+        <v>38</v>
+      </c>
+      <c r="G468" t="s">
+        <v>34</v>
+      </c>
+      <c r="H468" t="s">
+        <v>35</v>
+      </c>
+      <c r="K468">
+        <v>43</v>
+      </c>
+      <c r="L468">
+        <v>1.1627909999999999</v>
+      </c>
+      <c r="N468" t="s">
+        <v>52</v>
+      </c>
+      <c r="O468">
+        <v>0</v>
+      </c>
+      <c r="P468">
+        <v>12</v>
+      </c>
+      <c r="Q468" t="s">
+        <v>220</v>
+      </c>
+      <c r="R468">
+        <v>50</v>
+      </c>
+      <c r="S468">
+        <v>240</v>
+      </c>
+      <c r="X468">
+        <v>0</v>
+      </c>
+      <c r="Y468">
+        <v>0</v>
+      </c>
+      <c r="Z468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A469" t="s">
+        <v>28</v>
+      </c>
+      <c r="B469" t="s">
+        <v>29</v>
+      </c>
+      <c r="C469" t="s">
+        <v>221</v>
+      </c>
+      <c r="D469" t="s">
+        <v>31</v>
+      </c>
+      <c r="E469" t="s">
+        <v>41</v>
+      </c>
+      <c r="F469" t="s">
+        <v>38</v>
+      </c>
+      <c r="G469" t="s">
+        <v>34</v>
+      </c>
+      <c r="H469" t="s">
+        <v>35</v>
+      </c>
+      <c r="I469">
+        <v>117</v>
+      </c>
+      <c r="J469" t="s">
+        <v>51</v>
+      </c>
+      <c r="K469">
+        <v>2280</v>
+      </c>
+      <c r="L469">
+        <v>1.5850880000000001</v>
+      </c>
+      <c r="M469">
+        <v>49.401709400000001</v>
+      </c>
+      <c r="N469" t="s">
+        <v>52</v>
+      </c>
+      <c r="O469">
+        <v>0</v>
+      </c>
+      <c r="P469">
+        <v>5780</v>
+      </c>
+      <c r="Q469" t="s">
+        <v>220</v>
+      </c>
+      <c r="R469">
+        <v>3614</v>
+      </c>
+      <c r="S469">
+        <v>1599.335916</v>
+      </c>
+      <c r="T469">
+        <v>124</v>
+      </c>
+      <c r="V469">
+        <v>46.612903000000003</v>
+      </c>
+      <c r="W469">
+        <v>3.431101</v>
+      </c>
+      <c r="X469">
+        <v>152</v>
+      </c>
+      <c r="Y469">
+        <v>4.2058660000000003</v>
+      </c>
+      <c r="Z469">
+        <v>38.026316000000001</v>
+      </c>
+      <c r="AA469">
+        <v>117</v>
+      </c>
+      <c r="AB469">
+        <v>49.401708999999997</v>
+      </c>
+    </row>
+    <row r="470" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A470" t="s">
+        <v>28</v>
+      </c>
+      <c r="B470" t="s">
+        <v>29</v>
+      </c>
+      <c r="C470" t="s">
+        <v>221</v>
+      </c>
+      <c r="D470" t="s">
+        <v>31</v>
+      </c>
+      <c r="E470" t="s">
+        <v>42</v>
+      </c>
+      <c r="F470" t="s">
+        <v>38</v>
+      </c>
+      <c r="G470" t="s">
+        <v>34</v>
+      </c>
+      <c r="H470" t="s">
+        <v>35</v>
+      </c>
+      <c r="I470">
+        <v>202</v>
+      </c>
+      <c r="J470" t="s">
+        <v>51</v>
+      </c>
+      <c r="K470">
+        <v>3003</v>
+      </c>
+      <c r="L470">
+        <v>1.3466530000000001</v>
+      </c>
+      <c r="M470">
+        <v>48.722772280000001</v>
+      </c>
+      <c r="N470" t="s">
+        <v>52</v>
+      </c>
+      <c r="O470">
+        <v>0</v>
+      </c>
+      <c r="P470">
+        <v>9842</v>
+      </c>
+      <c r="Q470" t="s">
+        <v>220</v>
+      </c>
+      <c r="R470">
+        <v>4044</v>
+      </c>
+      <c r="S470">
+        <v>2433.7289810000002</v>
+      </c>
+      <c r="T470">
+        <v>224</v>
+      </c>
+      <c r="V470">
+        <v>43.9375</v>
+      </c>
+      <c r="W470">
+        <v>5.5390699999999997</v>
+      </c>
+      <c r="X470">
+        <v>239</v>
+      </c>
+      <c r="Y470">
+        <v>5.9099899999999996</v>
+      </c>
+      <c r="Z470">
+        <v>41.179915999999999</v>
+      </c>
+      <c r="AA470">
+        <v>202</v>
+      </c>
+      <c r="AB470">
+        <v>48.722771999999999</v>
+      </c>
+    </row>
+    <row r="471" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A471" t="s">
+        <v>28</v>
+      </c>
+      <c r="B471" t="s">
+        <v>29</v>
+      </c>
+      <c r="C471" t="s">
+        <v>219</v>
+      </c>
+      <c r="D471" t="s">
+        <v>31</v>
+      </c>
+      <c r="E471" t="s">
+        <v>32</v>
+      </c>
+      <c r="F471" t="s">
+        <v>38</v>
+      </c>
+      <c r="G471" t="s">
+        <v>34</v>
+      </c>
+      <c r="H471" t="s">
+        <v>35</v>
+      </c>
+      <c r="I471">
+        <v>59</v>
+      </c>
+      <c r="J471" t="s">
+        <v>51</v>
+      </c>
+      <c r="K471">
+        <v>3663</v>
+      </c>
+      <c r="L471">
+        <v>1.214305</v>
+      </c>
+      <c r="M471">
+        <v>78.644067800000002</v>
+      </c>
+      <c r="N471" t="s">
+        <v>52</v>
+      </c>
+      <c r="O471">
+        <v>0</v>
+      </c>
+      <c r="P471">
+        <v>4640</v>
+      </c>
+      <c r="Q471" t="s">
+        <v>70</v>
+      </c>
+      <c r="R471">
+        <v>4448</v>
+      </c>
+      <c r="S471">
+        <v>1043.1654679999999</v>
+      </c>
+      <c r="T471">
+        <v>106</v>
+      </c>
+      <c r="V471">
+        <v>43.773584999999997</v>
+      </c>
+      <c r="W471">
+        <v>2.3830939999999998</v>
+      </c>
+      <c r="X471">
+        <v>118</v>
+      </c>
+      <c r="Y471">
+        <v>2.6528779999999998</v>
+      </c>
+      <c r="Z471">
+        <v>39.322034000000002</v>
+      </c>
+      <c r="AA471">
+        <v>59</v>
+      </c>
+      <c r="AB471">
+        <v>78.644068000000004</v>
+      </c>
+    </row>
+    <row r="472" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A472" t="s">
+        <v>28</v>
+      </c>
+      <c r="B472" t="s">
+        <v>29</v>
+      </c>
+      <c r="C472" t="s">
+        <v>219</v>
+      </c>
+      <c r="D472" t="s">
+        <v>31</v>
+      </c>
+      <c r="E472" t="s">
+        <v>41</v>
+      </c>
+      <c r="F472" t="s">
+        <v>38</v>
+      </c>
+      <c r="G472" t="s">
+        <v>34</v>
+      </c>
+      <c r="H472" t="s">
+        <v>35</v>
+      </c>
+      <c r="K472">
+        <v>19</v>
+      </c>
+      <c r="L472">
+        <v>1.052632</v>
+      </c>
+      <c r="N472" t="s">
+        <v>52</v>
+      </c>
+      <c r="O472">
+        <v>0</v>
+      </c>
+      <c r="P472">
+        <v>25</v>
+      </c>
+      <c r="Q472" t="s">
+        <v>70</v>
+      </c>
+      <c r="R472">
+        <v>20</v>
+      </c>
+      <c r="S472">
+        <v>1250</v>
+      </c>
+      <c r="X472">
+        <v>1</v>
+      </c>
+      <c r="Y472">
+        <v>5</v>
+      </c>
+      <c r="Z472">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="473" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A473" t="s">
+        <v>28</v>
+      </c>
+      <c r="B473" t="s">
+        <v>29</v>
+      </c>
+      <c r="C473" t="s">
+        <v>219</v>
+      </c>
+      <c r="D473" t="s">
+        <v>31</v>
+      </c>
+      <c r="E473" t="s">
+        <v>42</v>
+      </c>
+      <c r="F473" t="s">
+        <v>38</v>
+      </c>
+      <c r="G473" t="s">
+        <v>34</v>
+      </c>
+      <c r="H473" t="s">
+        <v>35</v>
+      </c>
+      <c r="K473">
+        <v>1</v>
+      </c>
+      <c r="L473">
+        <v>1</v>
+      </c>
+      <c r="N473" t="s">
+        <v>52</v>
+      </c>
+      <c r="O473">
+        <v>0</v>
+      </c>
+      <c r="P473">
+        <v>1</v>
+      </c>
+      <c r="Q473" t="s">
+        <v>70</v>
+      </c>
+      <c r="R473">
+        <v>1</v>
+      </c>
+      <c r="S473">
+        <v>1000</v>
+      </c>
+      <c r="X473">
+        <v>0</v>
+      </c>
+      <c r="Y473">
+        <v>0</v>
+      </c>
+      <c r="Z473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A474" t="s">
+        <v>28</v>
+      </c>
+      <c r="B474" t="s">
+        <v>29</v>
+      </c>
+      <c r="C474" t="s">
+        <v>218</v>
+      </c>
+      <c r="D474" t="s">
+        <v>31</v>
+      </c>
+      <c r="E474" t="s">
+        <v>32</v>
+      </c>
+      <c r="F474" t="s">
+        <v>38</v>
+      </c>
+      <c r="G474" t="s">
+        <v>34</v>
+      </c>
+      <c r="H474" t="s">
+        <v>35</v>
+      </c>
+      <c r="I474">
+        <v>8</v>
+      </c>
+      <c r="J474" t="s">
+        <v>51</v>
+      </c>
+      <c r="K474">
+        <v>876</v>
+      </c>
+      <c r="L474">
+        <v>1.231735</v>
+      </c>
+      <c r="M474">
+        <v>77.25</v>
+      </c>
+      <c r="N474" t="s">
+        <v>52</v>
+      </c>
+      <c r="O474">
+        <v>0</v>
+      </c>
+      <c r="P474">
+        <v>618</v>
+      </c>
+      <c r="Q474" t="s">
+        <v>70</v>
+      </c>
+      <c r="R474">
+        <v>1079</v>
+      </c>
+      <c r="S474">
+        <v>572.75254900000004</v>
+      </c>
+      <c r="T474">
+        <v>10</v>
+      </c>
+      <c r="V474">
+        <v>61.8</v>
+      </c>
+      <c r="W474">
+        <v>0.92678400000000005</v>
+      </c>
+      <c r="X474">
+        <v>14</v>
+      </c>
+      <c r="Y474">
+        <v>1.297498</v>
+      </c>
+      <c r="Z474">
+        <v>44.142856999999999</v>
+      </c>
+      <c r="AA474">
+        <v>8</v>
+      </c>
+      <c r="AB474">
+        <v>77.25</v>
+      </c>
+    </row>
+    <row r="475" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A475" t="s">
+        <v>28</v>
+      </c>
+      <c r="B475" t="s">
+        <v>29</v>
+      </c>
+      <c r="C475" t="s">
+        <v>218</v>
+      </c>
+      <c r="D475" t="s">
+        <v>31</v>
+      </c>
+      <c r="E475" t="s">
+        <v>41</v>
+      </c>
+      <c r="F475" t="s">
+        <v>38</v>
+      </c>
+      <c r="G475" t="s">
+        <v>34</v>
+      </c>
+      <c r="H475" t="s">
+        <v>35</v>
+      </c>
+      <c r="I475">
+        <v>11</v>
+      </c>
+      <c r="J475" t="s">
+        <v>51</v>
+      </c>
+      <c r="K475">
+        <v>1216</v>
+      </c>
+      <c r="L475">
+        <v>1.193257</v>
+      </c>
+      <c r="M475">
+        <v>75.636363639999999</v>
+      </c>
+      <c r="N475" t="s">
+        <v>52</v>
+      </c>
+      <c r="O475">
+        <v>0</v>
+      </c>
+      <c r="P475">
+        <v>832</v>
+      </c>
+      <c r="Q475" t="s">
+        <v>70</v>
+      </c>
+      <c r="R475">
+        <v>1451</v>
+      </c>
+      <c r="S475">
+        <v>573.39765699999998</v>
+      </c>
+      <c r="T475">
+        <v>11</v>
+      </c>
+      <c r="V475">
+        <v>75.636364</v>
+      </c>
+      <c r="W475">
+        <v>0.75809800000000005</v>
+      </c>
+      <c r="X475">
+        <v>22</v>
+      </c>
+      <c r="Y475">
+        <v>1.5161960000000001</v>
+      </c>
+      <c r="Z475">
+        <v>37.818182</v>
+      </c>
+      <c r="AA475">
+        <v>11</v>
+      </c>
+      <c r="AB475">
+        <v>75.636364</v>
+      </c>
+    </row>
+    <row r="476" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A476" t="s">
+        <v>28</v>
+      </c>
+      <c r="B476" t="s">
+        <v>29</v>
+      </c>
+      <c r="C476" t="s">
+        <v>218</v>
+      </c>
+      <c r="D476" t="s">
+        <v>31</v>
+      </c>
+      <c r="E476" t="s">
+        <v>42</v>
+      </c>
+      <c r="F476" t="s">
+        <v>38</v>
+      </c>
+      <c r="G476" t="s">
+        <v>34</v>
+      </c>
+      <c r="H476" t="s">
+        <v>35</v>
+      </c>
+      <c r="I476">
+        <v>81</v>
+      </c>
+      <c r="J476" t="s">
+        <v>51</v>
+      </c>
+      <c r="K476">
+        <v>2455</v>
+      </c>
+      <c r="L476">
+        <v>1.3315680000000001</v>
+      </c>
+      <c r="M476">
+        <v>44.567901229999997</v>
+      </c>
+      <c r="N476" t="s">
+        <v>52</v>
+      </c>
+      <c r="O476">
+        <v>0</v>
+      </c>
+      <c r="P476">
+        <v>3610</v>
+      </c>
+      <c r="Q476" t="s">
+        <v>70</v>
+      </c>
+      <c r="R476">
+        <v>3269</v>
+      </c>
+      <c r="S476">
+        <v>1104.3132459999999</v>
+      </c>
+      <c r="T476">
+        <v>93</v>
+      </c>
+      <c r="V476">
+        <v>38.817203999999997</v>
+      </c>
+      <c r="W476">
+        <v>2.8449070000000001</v>
+      </c>
+      <c r="X476">
+        <v>96</v>
+      </c>
+      <c r="Y476">
+        <v>2.9366780000000001</v>
+      </c>
+      <c r="Z476">
+        <v>37.604166999999997</v>
+      </c>
+      <c r="AA476">
+        <v>81</v>
+      </c>
+      <c r="AB476">
+        <v>44.567900999999999</v>
+      </c>
+    </row>
+    <row r="477" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A477" t="s">
+        <v>28</v>
+      </c>
+      <c r="B477" t="s">
+        <v>29</v>
+      </c>
+      <c r="C477" t="s">
+        <v>217</v>
+      </c>
+      <c r="D477" t="s">
+        <v>31</v>
+      </c>
+      <c r="E477" t="s">
+        <v>32</v>
+      </c>
+      <c r="F477" t="s">
+        <v>38</v>
+      </c>
+      <c r="G477" t="s">
+        <v>216</v>
+      </c>
+      <c r="H477" t="s">
+        <v>35</v>
+      </c>
+      <c r="K477">
+        <v>34</v>
+      </c>
+      <c r="L477">
+        <v>1.029412</v>
+      </c>
+      <c r="N477" t="s">
+        <v>52</v>
+      </c>
+      <c r="O477">
+        <v>0</v>
+      </c>
+      <c r="P477">
+        <v>33</v>
+      </c>
+      <c r="Q477" t="s">
+        <v>215</v>
+      </c>
+      <c r="R477">
+        <v>35</v>
+      </c>
+      <c r="S477">
+        <v>942.85714299999995</v>
+      </c>
+      <c r="T477">
+        <v>1</v>
+      </c>
+      <c r="V477">
+        <v>33</v>
+      </c>
+      <c r="W477">
+        <v>2.8571430000000002</v>
+      </c>
+      <c r="X477">
+        <v>2</v>
+      </c>
+      <c r="Y477">
+        <v>5.7142860000000004</v>
+      </c>
+      <c r="Z477">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="478" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A478" t="s">
+        <v>28</v>
+      </c>
+      <c r="B478" t="s">
+        <v>29</v>
+      </c>
+      <c r="C478" t="s">
+        <v>217</v>
+      </c>
+      <c r="D478" t="s">
+        <v>31</v>
+      </c>
+      <c r="E478" t="s">
+        <v>41</v>
+      </c>
+      <c r="F478" t="s">
+        <v>38</v>
+      </c>
+      <c r="G478" t="s">
+        <v>216</v>
+      </c>
+      <c r="H478" t="s">
+        <v>35</v>
+      </c>
+      <c r="K478">
+        <v>4</v>
+      </c>
+      <c r="L478">
+        <v>1</v>
+      </c>
+      <c r="N478" t="s">
+        <v>52</v>
+      </c>
+      <c r="O478">
+        <v>0</v>
+      </c>
+      <c r="P478">
+        <v>6</v>
+      </c>
+      <c r="Q478" t="s">
+        <v>215</v>
+      </c>
+      <c r="R478">
+        <v>4</v>
+      </c>
+      <c r="S478">
+        <v>1500</v>
+      </c>
+      <c r="X478">
+        <v>0</v>
+      </c>
+      <c r="Y478">
+        <v>0</v>
+      </c>
+      <c r="Z478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A479" t="s">
+        <v>28</v>
+      </c>
+      <c r="B479" t="s">
+        <v>29</v>
+      </c>
+      <c r="C479" t="s">
+        <v>217</v>
+      </c>
+      <c r="D479" t="s">
+        <v>31</v>
+      </c>
+      <c r="E479" t="s">
+        <v>42</v>
+      </c>
+      <c r="F479" t="s">
+        <v>38</v>
+      </c>
+      <c r="G479" t="s">
+        <v>216</v>
+      </c>
+      <c r="H479" t="s">
+        <v>35</v>
+      </c>
+      <c r="K479">
+        <v>179</v>
+      </c>
+      <c r="L479">
+        <v>1.0111730000000001</v>
+      </c>
+      <c r="N479" t="s">
+        <v>52</v>
+      </c>
+      <c r="O479">
+        <v>0</v>
+      </c>
+      <c r="P479">
+        <v>221</v>
+      </c>
+      <c r="Q479" t="s">
+        <v>215</v>
+      </c>
+      <c r="R479">
+        <v>181</v>
+      </c>
+      <c r="S479">
+        <v>1220.994475</v>
+      </c>
+      <c r="X479">
+        <v>0</v>
+      </c>
+      <c r="Y479">
+        <v>0</v>
+      </c>
+      <c r="Z479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A480" t="s">
+        <v>28</v>
+      </c>
+      <c r="B480" t="s">
+        <v>29</v>
+      </c>
+      <c r="C480" t="s">
+        <v>214</v>
+      </c>
+      <c r="D480" t="s">
+        <v>31</v>
+      </c>
+      <c r="E480" t="s">
+        <v>32</v>
+      </c>
+      <c r="F480" t="s">
+        <v>38</v>
+      </c>
+      <c r="G480" t="s">
+        <v>34</v>
+      </c>
+      <c r="H480" t="s">
+        <v>35</v>
+      </c>
+      <c r="I480">
+        <v>43</v>
+      </c>
+      <c r="J480" t="s">
+        <v>51</v>
+      </c>
+      <c r="K480">
+        <v>4704</v>
+      </c>
+      <c r="L480">
+        <v>1.400298</v>
+      </c>
+      <c r="M480">
+        <v>130.74418605</v>
+      </c>
+      <c r="N480" t="s">
+        <v>52</v>
+      </c>
+      <c r="O480">
+        <v>0</v>
+      </c>
+      <c r="P480">
+        <v>5622</v>
+      </c>
+      <c r="Q480" t="s">
+        <v>78</v>
+      </c>
+      <c r="R480">
+        <v>6587</v>
+      </c>
+      <c r="S480">
+        <v>853.49931700000002</v>
+      </c>
+      <c r="T480">
+        <v>75</v>
+      </c>
+      <c r="V480">
+        <v>74.959999999999994</v>
+      </c>
+      <c r="W480">
+        <v>1.138606</v>
+      </c>
+      <c r="X480">
+        <v>85</v>
+      </c>
+      <c r="Y480">
+        <v>1.290421</v>
+      </c>
+      <c r="Z480">
+        <v>66.141176000000002</v>
+      </c>
+      <c r="AA480">
+        <v>43</v>
+      </c>
+      <c r="AB480">
+        <v>130.74418600000001</v>
+      </c>
+    </row>
+    <row r="481" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A481" t="s">
+        <v>28</v>
+      </c>
+      <c r="B481" t="s">
+        <v>29</v>
+      </c>
+      <c r="C481" t="s">
+        <v>214</v>
+      </c>
+      <c r="D481" t="s">
+        <v>31</v>
+      </c>
+      <c r="E481" t="s">
+        <v>42</v>
+      </c>
+      <c r="F481" t="s">
+        <v>38</v>
+      </c>
+      <c r="G481" t="s">
+        <v>34</v>
+      </c>
+      <c r="H481" t="s">
+        <v>35</v>
+      </c>
+      <c r="K481">
+        <v>4</v>
+      </c>
+      <c r="L481">
+        <v>1</v>
+      </c>
+      <c r="N481" t="s">
+        <v>52</v>
+      </c>
+      <c r="O481">
+        <v>0</v>
+      </c>
+      <c r="P481">
+        <v>8</v>
+      </c>
+      <c r="Q481" t="s">
+        <v>78</v>
+      </c>
+      <c r="R481">
+        <v>4</v>
+      </c>
+      <c r="S481">
+        <v>2000</v>
+      </c>
+      <c r="X481">
+        <v>0</v>
+      </c>
+      <c r="Y481">
+        <v>0</v>
+      </c>
+      <c r="Z481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A482" t="s">
+        <v>28</v>
+      </c>
+      <c r="B482" t="s">
+        <v>29</v>
+      </c>
+      <c r="C482" t="s">
+        <v>213</v>
+      </c>
+      <c r="D482" t="s">
+        <v>31</v>
+      </c>
+      <c r="E482" t="s">
+        <v>32</v>
+      </c>
+      <c r="F482" t="s">
+        <v>38</v>
+      </c>
+      <c r="G482" t="s">
+        <v>34</v>
+      </c>
+      <c r="H482" t="s">
+        <v>35</v>
+      </c>
+      <c r="I482">
+        <v>39</v>
+      </c>
+      <c r="J482" t="s">
+        <v>51</v>
+      </c>
+      <c r="K482">
+        <v>1341</v>
+      </c>
+      <c r="L482">
+        <v>1.46607</v>
+      </c>
+      <c r="M482">
+        <v>37.410256410000002</v>
+      </c>
+      <c r="N482" t="s">
+        <v>52</v>
+      </c>
+      <c r="O482">
+        <v>0</v>
+      </c>
+      <c r="P482">
+        <v>1459</v>
+      </c>
+      <c r="Q482" t="s">
+        <v>78</v>
+      </c>
+      <c r="R482">
+        <v>1966</v>
+      </c>
+      <c r="S482">
+        <v>742.11597200000006</v>
+      </c>
+      <c r="T482">
+        <v>42</v>
+      </c>
+      <c r="V482">
+        <v>34.738095000000001</v>
+      </c>
+      <c r="W482">
+        <v>2.136317</v>
+      </c>
+      <c r="X482">
+        <v>55</v>
+      </c>
+      <c r="Y482">
+        <v>2.797558</v>
+      </c>
+      <c r="Z482">
+        <v>26.527273000000001</v>
+      </c>
+      <c r="AA482">
+        <v>39</v>
+      </c>
+      <c r="AB482">
+        <v>37.410255999999997</v>
+      </c>
+    </row>
+    <row r="483" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A483" t="s">
+        <v>28</v>
+      </c>
+      <c r="B483" t="s">
+        <v>29</v>
+      </c>
+      <c r="C483" t="s">
+        <v>213</v>
+      </c>
+      <c r="D483" t="s">
+        <v>31</v>
+      </c>
+      <c r="E483" t="s">
+        <v>41</v>
+      </c>
+      <c r="F483" t="s">
+        <v>38</v>
+      </c>
+      <c r="G483" t="s">
+        <v>34</v>
+      </c>
+      <c r="H483" t="s">
+        <v>35</v>
+      </c>
+      <c r="I483">
+        <v>101</v>
+      </c>
+      <c r="J483" t="s">
+        <v>51</v>
+      </c>
+      <c r="K483">
+        <v>2152</v>
+      </c>
+      <c r="L483">
+        <v>1.434944</v>
+      </c>
+      <c r="M483">
+        <v>25.940594059999999</v>
+      </c>
+      <c r="N483" t="s">
+        <v>52</v>
+      </c>
+      <c r="O483">
+        <v>0</v>
+      </c>
+      <c r="P483">
+        <v>2620</v>
+      </c>
+      <c r="Q483" t="s">
+        <v>78</v>
+      </c>
+      <c r="R483">
+        <v>3088</v>
+      </c>
+      <c r="S483">
+        <v>848.44559600000002</v>
+      </c>
+      <c r="T483">
+        <v>118</v>
+      </c>
+      <c r="V483">
+        <v>22.203389999999999</v>
+      </c>
+      <c r="W483">
+        <v>3.8212440000000001</v>
+      </c>
+      <c r="X483">
+        <v>154</v>
+      </c>
+      <c r="Y483">
+        <v>4.9870469999999996</v>
+      </c>
+      <c r="Z483">
+        <v>17.012986999999999</v>
+      </c>
+      <c r="AA483">
+        <v>101</v>
+      </c>
+      <c r="AB483">
+        <v>25.940594000000001</v>
+      </c>
+    </row>
+    <row r="484" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A484" t="s">
+        <v>28</v>
+      </c>
+      <c r="B484" t="s">
+        <v>29</v>
+      </c>
+      <c r="C484" t="s">
+        <v>213</v>
+      </c>
+      <c r="D484" t="s">
+        <v>31</v>
+      </c>
+      <c r="E484" t="s">
+        <v>42</v>
+      </c>
+      <c r="F484" t="s">
+        <v>38</v>
+      </c>
+      <c r="G484" t="s">
+        <v>34</v>
+      </c>
+      <c r="H484" t="s">
+        <v>35</v>
+      </c>
+      <c r="I484">
+        <v>39</v>
+      </c>
+      <c r="J484" t="s">
+        <v>51</v>
+      </c>
+      <c r="K484">
+        <v>969</v>
+      </c>
+      <c r="L484">
+        <v>1.224974</v>
+      </c>
+      <c r="M484">
+        <v>36.717948720000003</v>
+      </c>
+      <c r="N484" t="s">
+        <v>52</v>
+      </c>
+      <c r="O484">
+        <v>0</v>
+      </c>
+      <c r="P484">
+        <v>1432</v>
+      </c>
+      <c r="Q484" t="s">
+        <v>78</v>
+      </c>
+      <c r="R484">
+        <v>1187</v>
+      </c>
+      <c r="S484">
+        <v>1206.4026960000001</v>
+      </c>
+      <c r="T484">
+        <v>42</v>
+      </c>
+      <c r="V484">
+        <v>34.095238000000002</v>
+      </c>
+      <c r="W484">
+        <v>3.538332</v>
+      </c>
+      <c r="X484">
+        <v>48</v>
+      </c>
+      <c r="Y484">
+        <v>4.0438080000000003</v>
+      </c>
+      <c r="Z484">
+        <v>29.833333</v>
+      </c>
+      <c r="AA484">
+        <v>39</v>
+      </c>
+      <c r="AB484">
+        <v>36.717948999999997</v>
+      </c>
+    </row>
+    <row r="485" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A485" t="s">
+        <v>28</v>
+      </c>
+      <c r="B485" t="s">
+        <v>29</v>
+      </c>
+      <c r="C485" t="s">
+        <v>212</v>
+      </c>
+      <c r="D485" t="s">
+        <v>31</v>
+      </c>
+      <c r="E485" t="s">
+        <v>32</v>
+      </c>
+      <c r="F485" t="s">
+        <v>38</v>
+      </c>
+      <c r="G485" t="s">
+        <v>118</v>
+      </c>
+      <c r="H485" t="s">
+        <v>35</v>
+      </c>
+      <c r="I485">
+        <v>7</v>
+      </c>
+      <c r="J485" t="s">
+        <v>51</v>
+      </c>
+      <c r="K485">
+        <v>502</v>
+      </c>
+      <c r="L485">
+        <v>1.0916330000000001</v>
+      </c>
+      <c r="M485">
+        <v>55.571428570000002</v>
+      </c>
+      <c r="N485" t="s">
+        <v>52</v>
+      </c>
+      <c r="O485">
+        <v>0</v>
+      </c>
+      <c r="P485">
+        <v>389</v>
+      </c>
+      <c r="Q485" t="s">
+        <v>82</v>
+      </c>
+      <c r="R485">
+        <v>548</v>
+      </c>
+      <c r="S485">
+        <v>709.854015</v>
+      </c>
+      <c r="T485">
+        <v>9</v>
+      </c>
+      <c r="V485">
+        <v>43.222222000000002</v>
+      </c>
+      <c r="W485">
+        <v>1.642336</v>
+      </c>
+      <c r="X485">
+        <v>15</v>
+      </c>
+      <c r="Y485">
+        <v>2.7372260000000002</v>
+      </c>
+      <c r="Z485">
+        <v>25.933333000000001</v>
+      </c>
+      <c r="AA485">
+        <v>7</v>
+      </c>
+      <c r="AB485">
+        <v>55.571429000000002</v>
+      </c>
+    </row>
+    <row r="486" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A486" t="s">
+        <v>28</v>
+      </c>
+      <c r="B486" t="s">
+        <v>29</v>
+      </c>
+      <c r="C486" t="s">
+        <v>212</v>
+      </c>
+      <c r="D486" t="s">
+        <v>31</v>
+      </c>
+      <c r="E486" t="s">
+        <v>40</v>
+      </c>
+      <c r="F486" t="s">
+        <v>38</v>
+      </c>
+      <c r="G486" t="s">
+        <v>118</v>
+      </c>
+      <c r="H486" t="s">
+        <v>35</v>
+      </c>
+      <c r="K486">
+        <v>1</v>
+      </c>
+      <c r="L486">
+        <v>1</v>
+      </c>
+      <c r="N486" t="s">
+        <v>52</v>
+      </c>
+      <c r="O486">
+        <v>0</v>
+      </c>
+      <c r="P486">
+        <v>0</v>
+      </c>
+      <c r="Q486" t="s">
+        <v>82</v>
+      </c>
+      <c r="R486">
+        <v>1</v>
+      </c>
+      <c r="S486">
+        <v>0</v>
+      </c>
+      <c r="X486">
+        <v>0</v>
+      </c>
+      <c r="Y486">
+        <v>0</v>
+      </c>
+      <c r="Z486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A487" t="s">
+        <v>28</v>
+      </c>
+      <c r="B487" t="s">
+        <v>29</v>
+      </c>
+      <c r="C487" t="s">
+        <v>212</v>
+      </c>
+      <c r="D487" t="s">
+        <v>31</v>
+      </c>
+      <c r="E487" t="s">
+        <v>41</v>
+      </c>
+      <c r="F487" t="s">
+        <v>38</v>
+      </c>
+      <c r="G487" t="s">
+        <v>118</v>
+      </c>
+      <c r="H487" t="s">
+        <v>35</v>
+      </c>
+      <c r="I487">
+        <v>3</v>
+      </c>
+      <c r="J487" t="s">
+        <v>51</v>
+      </c>
+      <c r="K487">
+        <v>424</v>
+      </c>
+      <c r="L487">
+        <v>1.0566040000000001</v>
+      </c>
+      <c r="M487">
+        <v>118.33333333</v>
+      </c>
+      <c r="N487" t="s">
+        <v>52</v>
+      </c>
+      <c r="O487">
+        <v>0</v>
+      </c>
+      <c r="P487">
+        <v>355</v>
+      </c>
+      <c r="Q487" t="s">
+        <v>82</v>
+      </c>
+      <c r="R487">
+        <v>448</v>
+      </c>
+      <c r="S487">
+        <v>792.41071399999998</v>
+      </c>
+      <c r="T487">
+        <v>6</v>
+      </c>
+      <c r="V487">
+        <v>59.166666999999997</v>
+      </c>
+      <c r="W487">
+        <v>1.339286</v>
+      </c>
+      <c r="X487">
+        <v>7</v>
+      </c>
+      <c r="Y487">
+        <v>1.5625</v>
+      </c>
+      <c r="Z487">
+        <v>50.714286000000001</v>
+      </c>
+      <c r="AA487">
+        <v>3</v>
+      </c>
+      <c r="AB487">
+        <v>118.333333</v>
+      </c>
+    </row>
+    <row r="488" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A488" t="s">
+        <v>28</v>
+      </c>
+      <c r="B488" t="s">
+        <v>29</v>
+      </c>
+      <c r="C488" t="s">
+        <v>212</v>
+      </c>
+      <c r="D488" t="s">
+        <v>31</v>
+      </c>
+      <c r="E488" t="s">
+        <v>42</v>
+      </c>
+      <c r="F488" t="s">
+        <v>38</v>
+      </c>
+      <c r="G488" t="s">
+        <v>118</v>
+      </c>
+      <c r="H488" t="s">
+        <v>35</v>
+      </c>
+      <c r="I488">
+        <v>14</v>
+      </c>
+      <c r="J488" t="s">
+        <v>51</v>
+      </c>
+      <c r="K488">
+        <v>620</v>
+      </c>
+      <c r="L488">
+        <v>1.058065</v>
+      </c>
+      <c r="M488">
+        <v>64.928571430000005</v>
+      </c>
+      <c r="N488" t="s">
+        <v>52</v>
+      </c>
+      <c r="O488">
+        <v>0</v>
+      </c>
+      <c r="P488">
+        <v>909</v>
+      </c>
+      <c r="Q488" t="s">
+        <v>82</v>
+      </c>
+      <c r="R488">
+        <v>656</v>
+      </c>
+      <c r="S488">
+        <v>1385.670732</v>
+      </c>
+      <c r="T488">
+        <v>14</v>
+      </c>
+      <c r="V488">
+        <v>64.928571000000005</v>
+      </c>
+      <c r="W488">
+        <v>2.1341459999999999</v>
+      </c>
+      <c r="X488">
+        <v>22</v>
+      </c>
+      <c r="Y488">
+        <v>3.3536589999999999</v>
+      </c>
+      <c r="Z488">
+        <v>41.318182</v>
+      </c>
+      <c r="AA488">
+        <v>14</v>
+      </c>
+      <c r="AB488">
+        <v>64.928571000000005</v>
+      </c>
+    </row>
+    <row r="489" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A489" t="s">
+        <v>28</v>
+      </c>
+      <c r="B489" t="s">
+        <v>29</v>
+      </c>
+      <c r="C489" t="s">
+        <v>211</v>
+      </c>
+      <c r="D489" t="s">
+        <v>31</v>
+      </c>
+      <c r="E489" t="s">
+        <v>32</v>
+      </c>
+      <c r="F489" t="s">
+        <v>38</v>
+      </c>
+      <c r="G489" t="s">
+        <v>34</v>
+      </c>
+      <c r="H489" t="s">
+        <v>35</v>
+      </c>
+      <c r="I489">
+        <v>25</v>
+      </c>
+      <c r="J489" t="s">
+        <v>51</v>
+      </c>
+      <c r="K489">
+        <v>1355</v>
+      </c>
+      <c r="L489">
+        <v>1.2583029999999999</v>
+      </c>
+      <c r="M489">
+        <v>71.44</v>
+      </c>
+      <c r="N489" t="s">
+        <v>52</v>
+      </c>
+      <c r="O489">
+        <v>0</v>
+      </c>
+      <c r="P489">
+        <v>1786</v>
+      </c>
+      <c r="Q489" t="s">
+        <v>210</v>
+      </c>
+      <c r="R489">
+        <v>1705</v>
+      </c>
+      <c r="S489">
+        <v>1047.507331</v>
+      </c>
+      <c r="T489">
+        <v>31</v>
+      </c>
+      <c r="V489">
+        <v>57.612903000000003</v>
+      </c>
+      <c r="W489">
+        <v>1.818182</v>
+      </c>
+      <c r="X489">
+        <v>35</v>
+      </c>
+      <c r="Y489">
+        <v>2.0527860000000002</v>
+      </c>
+      <c r="Z489">
+        <v>51.028570999999999</v>
+      </c>
+      <c r="AA489">
+        <v>25</v>
+      </c>
+      <c r="AB489">
+        <v>71.44</v>
+      </c>
+    </row>
+    <row r="490" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A490" t="s">
+        <v>28</v>
+      </c>
+      <c r="B490" t="s">
+        <v>29</v>
+      </c>
+      <c r="C490" t="s">
+        <v>211</v>
+      </c>
+      <c r="D490" t="s">
+        <v>31</v>
+      </c>
+      <c r="E490" t="s">
+        <v>40</v>
+      </c>
+      <c r="F490" t="s">
+        <v>38</v>
+      </c>
+      <c r="G490" t="s">
+        <v>34</v>
+      </c>
+      <c r="H490" t="s">
+        <v>35</v>
+      </c>
+      <c r="K490">
+        <v>10</v>
+      </c>
+      <c r="L490">
+        <v>1</v>
+      </c>
+      <c r="N490" t="s">
+        <v>52</v>
+      </c>
+      <c r="O490">
+        <v>0</v>
+      </c>
+      <c r="P490">
+        <v>0</v>
+      </c>
+      <c r="Q490" t="s">
+        <v>210</v>
+      </c>
+      <c r="R490">
+        <v>10</v>
+      </c>
+      <c r="S490">
+        <v>0</v>
+      </c>
+      <c r="X490">
+        <v>0</v>
+      </c>
+      <c r="Y490">
+        <v>0</v>
+      </c>
+      <c r="Z490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A491" t="s">
+        <v>28</v>
+      </c>
+      <c r="B491" t="s">
+        <v>29</v>
+      </c>
+      <c r="C491" t="s">
+        <v>211</v>
+      </c>
+      <c r="D491" t="s">
+        <v>31</v>
+      </c>
+      <c r="E491" t="s">
+        <v>41</v>
+      </c>
+      <c r="F491" t="s">
+        <v>38</v>
+      </c>
+      <c r="G491" t="s">
+        <v>34</v>
+      </c>
+      <c r="H491" t="s">
+        <v>35</v>
+      </c>
+      <c r="I491">
+        <v>10</v>
+      </c>
+      <c r="J491" t="s">
+        <v>51</v>
+      </c>
+      <c r="K491">
+        <v>380</v>
+      </c>
+      <c r="L491">
+        <v>1.307895</v>
+      </c>
+      <c r="M491">
+        <v>56.4</v>
+      </c>
+      <c r="N491" t="s">
+        <v>52</v>
+      </c>
+      <c r="O491">
+        <v>0</v>
+      </c>
+      <c r="P491">
+        <v>564</v>
+      </c>
+      <c r="Q491" t="s">
+        <v>210</v>
+      </c>
+      <c r="R491">
+        <v>497</v>
+      </c>
+      <c r="S491">
+        <v>1134.808853</v>
+      </c>
+      <c r="T491">
+        <v>13</v>
+      </c>
+      <c r="V491">
+        <v>43.384614999999997</v>
+      </c>
+      <c r="W491">
+        <v>2.615694</v>
+      </c>
+      <c r="X491">
+        <v>14</v>
+      </c>
+      <c r="Y491">
+        <v>2.8169010000000001</v>
+      </c>
+      <c r="Z491">
+        <v>40.285713999999999</v>
+      </c>
+      <c r="AA491">
+        <v>10</v>
+      </c>
+      <c r="AB491">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="492" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A492" t="s">
+        <v>28</v>
+      </c>
+      <c r="B492" t="s">
+        <v>29</v>
+      </c>
+      <c r="C492" t="s">
+        <v>211</v>
+      </c>
+      <c r="D492" t="s">
+        <v>31</v>
+      </c>
+      <c r="E492" t="s">
+        <v>42</v>
+      </c>
+      <c r="F492" t="s">
+        <v>38</v>
+      </c>
+      <c r="G492" t="s">
+        <v>34</v>
+      </c>
+      <c r="H492" t="s">
+        <v>35</v>
+      </c>
+      <c r="I492">
+        <v>30</v>
+      </c>
+      <c r="J492" t="s">
+        <v>51</v>
+      </c>
+      <c r="K492">
+        <v>2354</v>
+      </c>
+      <c r="L492">
+        <v>1.1333899999999999</v>
+      </c>
+      <c r="M492">
+        <v>85</v>
+      </c>
+      <c r="N492" t="s">
+        <v>52</v>
+      </c>
+      <c r="O492">
+        <v>0</v>
+      </c>
+      <c r="P492">
+        <v>2550</v>
+      </c>
+      <c r="Q492" t="s">
+        <v>210</v>
+      </c>
+      <c r="R492">
+        <v>2668</v>
+      </c>
+      <c r="S492">
+        <v>955.77211399999999</v>
+      </c>
+      <c r="T492">
+        <v>34</v>
+      </c>
+      <c r="V492">
+        <v>75</v>
+      </c>
+      <c r="W492">
+        <v>1.2743629999999999</v>
+      </c>
+      <c r="X492">
+        <v>34</v>
+      </c>
+      <c r="Y492">
+        <v>1.2743629999999999</v>
+      </c>
+      <c r="Z492">
+        <v>75</v>
+      </c>
+      <c r="AA492">
+        <v>30</v>
+      </c>
+      <c r="AB492">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
